--- a/VUOT-TROI-2026.xlsx
+++ b/VUOT-TROI-2026.xlsx
@@ -959,7 +959,7 @@
       <c r="FP3" s="8" t="n"/>
       <c r="FQ3" s="5" t="inlineStr">
         <is>
-          <t>THÁNG 9 (data tới 22/09)</t>
+          <t>THÁNG 9</t>
         </is>
       </c>
       <c r="FR3" s="6" t="n"/>
@@ -2880,7 +2880,7 @@
         <v>3.63</v>
       </c>
       <c r="FR6" s="20" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="FS6" s="21" t="n">
         <v>4</v>
@@ -2889,7 +2889,7 @@
         <v>0.99</v>
       </c>
       <c r="FU6" s="22" t="n">
-        <v>0.9949</v>
+        <v>0.9968</v>
       </c>
       <c r="FV6" s="21" t="n">
         <v>2</v>
@@ -2898,7 +2898,7 @@
         <v>0.993</v>
       </c>
       <c r="FX6" s="22" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="FY6" s="21" t="n">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>53600000</v>
       </c>
       <c r="GG6" s="23" t="n">
-        <v>52414000</v>
+        <v>68724000</v>
       </c>
       <c r="GH6" s="21" t="n">
         <v>4</v>
@@ -3457,7 +3457,7 @@
         <v>3.63</v>
       </c>
       <c r="FR7" s="28" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="FS7" s="29" t="n">
         <v>4</v>
@@ -3466,7 +3466,7 @@
         <v>0.99</v>
       </c>
       <c r="FU7" s="30" t="n">
-        <v>0.9949</v>
+        <v>0.9968</v>
       </c>
       <c r="FV7" s="29" t="n">
         <v>2</v>
@@ -3475,7 +3475,7 @@
         <v>0.993</v>
       </c>
       <c r="FX7" s="30" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="FY7" s="29" t="n">
         <v>2</v>
@@ -3496,7 +3496,7 @@
         <v>53600000</v>
       </c>
       <c r="GG7" s="31" t="n">
-        <v>52414000</v>
+        <v>68724000</v>
       </c>
       <c r="GH7" s="29" t="n">
         <v>4</v>
@@ -4032,7 +4032,7 @@
         <v>3.63</v>
       </c>
       <c r="FR8" s="20" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="FS8" s="21" t="n">
         <v>4</v>
@@ -4041,7 +4041,7 @@
         <v>0.99</v>
       </c>
       <c r="FU8" s="22" t="n">
-        <v>0.9938</v>
+        <v>0.9954</v>
       </c>
       <c r="FV8" s="21" t="n">
         <v>2</v>
@@ -4050,7 +4050,7 @@
         <v>0.993</v>
       </c>
       <c r="FX8" s="22" t="n">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="FY8" s="21" t="n">
         <v>2</v>
@@ -4071,7 +4071,7 @@
         <v>51500000</v>
       </c>
       <c r="GG8" s="23" t="n">
-        <v>33490000</v>
+        <v>57360000</v>
       </c>
       <c r="GH8" s="21" t="n">
         <v>4</v>
@@ -4609,7 +4609,7 @@
         <v>3.63</v>
       </c>
       <c r="FR9" s="28" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="FS9" s="29" t="n">
         <v>4</v>
@@ -4618,7 +4618,7 @@
         <v>0.99</v>
       </c>
       <c r="FU9" s="30" t="n">
-        <v>0.9978</v>
+        <v>0.9971</v>
       </c>
       <c r="FV9" s="29" t="n">
         <v>2</v>
@@ -4627,7 +4627,7 @@
         <v>0.993</v>
       </c>
       <c r="FX9" s="30" t="n">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="FY9" s="29" t="n">
         <v>2</v>
@@ -4648,7 +4648,7 @@
         <v>33200000</v>
       </c>
       <c r="GG9" s="31" t="n">
-        <v>6380000</v>
+        <v>21190000</v>
       </c>
       <c r="GH9" s="29" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
         <v>3.63</v>
       </c>
       <c r="FR10" s="20" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="FS10" s="21" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
         <v>0.99</v>
       </c>
       <c r="FU10" s="22" t="n">
-        <v>0.9962</v>
+        <v>0.9969</v>
       </c>
       <c r="FV10" s="21" t="n">
         <v>2</v>
@@ -5225,7 +5225,7 @@
         <v>29600000</v>
       </c>
       <c r="GG10" s="23" t="n">
-        <v>9010000</v>
+        <v>15650000</v>
       </c>
       <c r="GH10" s="21" t="n">
         <v>0</v>
@@ -5257,7 +5257,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>18</v>
@@ -5272,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>3.63</v>
       </c>
       <c r="FR11" s="28" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="FS11" s="29" t="n">
         <v>0</v>
@@ -5772,10 +5772,10 @@
         <v>0.99</v>
       </c>
       <c r="FU11" s="30" t="n">
-        <v>0.9825</v>
+        <v>0.9908</v>
       </c>
       <c r="FV11" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FW11" s="30" t="n">
         <v>0.993</v>
@@ -5802,16 +5802,16 @@
         <v>11600000</v>
       </c>
       <c r="GG11" s="31" t="n">
-        <v>6070000</v>
+        <v>9370000</v>
       </c>
       <c r="GH11" s="29" t="n">
         <v>0</v>
       </c>
       <c r="GI11" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="GJ11" s="29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -5846,10 +5846,10 @@
         <v>16</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
@@ -6339,7 +6339,9 @@
       <c r="FQ12" s="20" t="n">
         <v>3.63</v>
       </c>
-      <c r="FR12" s="20" t="n"/>
+      <c r="FR12" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="FS12" s="21" t="n">
         <v>4</v>
       </c>
@@ -6356,7 +6358,7 @@
         <v>0.993</v>
       </c>
       <c r="FX12" s="22" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
       <c r="FY12" s="21" t="n">
         <v>2</v>
@@ -6377,36 +6379,36 @@
         <v>28600000</v>
       </c>
       <c r="GG12" s="23" t="n">
-        <v>14654000</v>
+        <v>30484000</v>
       </c>
       <c r="GH12" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="GI12" s="24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="GJ12" s="21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Hà Tĩnh</t>
+          <t>Quảng Nam</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Hùng Vương</t>
+          <t>Doãn Bá Tùng</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>18</v>
@@ -6415,16 +6417,16 @@
         <v>18</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I13" s="17" t="n">
         <v>18</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -6435,7 +6437,7 @@
         <v>4.3</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="O13" s="29" t="n">
         <v>4</v>
@@ -6477,10 +6479,10 @@
         <v>2</v>
       </c>
       <c r="AB13" s="31" t="n">
-        <v>7000000</v>
+        <v>14000000</v>
       </c>
       <c r="AC13" s="31" t="n">
-        <v>4500000</v>
+        <v>6750000</v>
       </c>
       <c r="AD13" s="29" t="n">
         <v>0</v>
@@ -6495,7 +6497,7 @@
         <v>4.3</v>
       </c>
       <c r="AH13" s="28" t="n">
-        <v>4.57</v>
+        <v>4.555000000000001</v>
       </c>
       <c r="AI13" s="29" t="n">
         <v>4</v>
@@ -6522,7 +6524,7 @@
         <v>0.9996</v>
       </c>
       <c r="AQ13" s="30" t="n">
-        <v>0.9988262910798122</v>
+        <v>0.9987915407854985</v>
       </c>
       <c r="AR13" s="29" t="n">
         <v>0</v>
@@ -6537,10 +6539,10 @@
         <v>2</v>
       </c>
       <c r="AV13" s="31" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="AW13" s="31" t="n">
-        <v>2100000</v>
+        <v>6150000</v>
       </c>
       <c r="AX13" s="29" t="n">
         <v>0</v>
@@ -6555,7 +6557,7 @@
         <v>3.36</v>
       </c>
       <c r="BB13" s="28" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="BC13" s="29" t="n">
         <v>4</v>
@@ -6582,10 +6584,10 @@
         <v>0.9997</v>
       </c>
       <c r="BK13" s="30" t="n">
-        <v>1</v>
+        <v>0.9994663820704376</v>
       </c>
       <c r="BL13" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM13" s="28" t="n">
         <v>10</v>
@@ -6597,25 +6599,25 @@
         <v>2</v>
       </c>
       <c r="BP13" s="31" t="n">
-        <v>6000000</v>
+        <v>11000000</v>
       </c>
       <c r="BQ13" s="31" t="n">
-        <v>4460000</v>
+        <v>8700000</v>
       </c>
       <c r="BR13" s="29" t="n">
         <v>0</v>
       </c>
       <c r="BS13" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BT13" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BU13" s="28" t="n">
         <v>3.4</v>
       </c>
       <c r="BV13" s="28" t="n">
-        <v>3.579448347200256</v>
+        <v>4.072024679485756</v>
       </c>
       <c r="BW13" s="29" t="n">
         <v>4</v>
@@ -6642,7 +6644,7 @@
         <v>0.9998</v>
       </c>
       <c r="CE13" s="30" t="n">
-        <v>0.9990281827016521</v>
+        <v>0.999479979199168</v>
       </c>
       <c r="CF13" s="29" t="n">
         <v>0</v>
@@ -6657,10 +6659,10 @@
         <v>2</v>
       </c>
       <c r="CJ13" s="31" t="n">
-        <v>6000000</v>
+        <v>13000000</v>
       </c>
       <c r="CK13" s="31" t="n">
-        <v>6330000</v>
+        <v>13350000</v>
       </c>
       <c r="CL13" s="29" t="n">
         <v>2</v>
@@ -6675,7 +6677,7 @@
         <v>3.44</v>
       </c>
       <c r="CP13" s="28" t="n">
-        <v>3.488179287726036</v>
+        <v>3.64152537159249</v>
       </c>
       <c r="CQ13" s="29" t="n">
         <v>4</v>
@@ -6717,10 +6719,10 @@
         <v>2</v>
       </c>
       <c r="DD13" s="31" t="n">
-        <v>8000000</v>
+        <v>16000000</v>
       </c>
       <c r="DE13" s="31" t="n">
-        <v>5250000</v>
+        <v>12450000</v>
       </c>
       <c r="DF13" s="29" t="n">
         <v>0</v>
@@ -6735,10 +6737,10 @@
         <v>3.18</v>
       </c>
       <c r="DJ13" s="28" t="n">
-        <v>2.99</v>
+        <v>4.42</v>
       </c>
       <c r="DK13" s="29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DL13" s="30" t="n">
         <v>1</v>
@@ -6777,25 +6779,25 @@
         <v>2</v>
       </c>
       <c r="DX13" s="31" t="n">
-        <v>20000000</v>
+        <v>50000000</v>
       </c>
       <c r="DY13" s="31" t="n">
-        <v>6030000</v>
+        <v>16130000</v>
       </c>
       <c r="DZ13" s="29" t="n">
         <v>0</v>
       </c>
       <c r="EA13" s="32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="EB13" s="29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="EC13" s="28" t="n">
         <v>3.23</v>
       </c>
       <c r="ED13" s="28" t="n">
-        <v>3.24</v>
+        <v>4.54</v>
       </c>
       <c r="EE13" s="29" t="n">
         <v>4</v>
@@ -6804,7 +6806,7 @@
         <v>0.97</v>
       </c>
       <c r="EG13" s="30" t="n">
-        <v>0.9848</v>
+        <v>0.9843</v>
       </c>
       <c r="EH13" s="29" t="n">
         <v>2</v>
@@ -6813,7 +6815,7 @@
         <v>0.991</v>
       </c>
       <c r="EJ13" s="30" t="n">
-        <v>1</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="EK13" s="29" t="n">
         <v>2</v>
@@ -6837,34 +6839,34 @@
         <v>2</v>
       </c>
       <c r="ER13" s="31" t="n">
-        <v>10800000</v>
+        <v>31000000</v>
       </c>
       <c r="ES13" s="31" t="n">
-        <v>16610000</v>
+        <v>25820000</v>
       </c>
       <c r="ET13" s="29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EU13" s="32" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="EV13" s="29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EW13" s="28" t="n">
         <v>3.6</v>
       </c>
       <c r="EX13" s="28" t="n">
-        <v>3.57</v>
+        <v>4.55</v>
       </c>
       <c r="EY13" s="29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="EZ13" s="30" t="n">
         <v>0.972</v>
       </c>
       <c r="FA13" s="30" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9853</v>
       </c>
       <c r="FB13" s="29" t="n">
         <v>2</v>
@@ -6897,13 +6899,13 @@
         <v>2</v>
       </c>
       <c r="FL13" s="31" t="n">
-        <v>11300000</v>
+        <v>32500000</v>
       </c>
       <c r="FM13" s="31" t="n">
-        <v>21958000</v>
+        <v>30910000</v>
       </c>
       <c r="FN13" s="29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="FO13" s="32" t="n">
         <v>12</v>
@@ -6915,16 +6917,16 @@
         <v>3.63</v>
       </c>
       <c r="FR13" s="28" t="n">
-        <v>3.26</v>
+        <v>4.35</v>
       </c>
       <c r="FS13" s="29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="FT13" s="30" t="n">
         <v>0.99</v>
       </c>
       <c r="FU13" s="30" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="FV13" s="29" t="n">
         <v>2</v>
@@ -6933,7 +6935,7 @@
         <v>0.993</v>
       </c>
       <c r="FX13" s="30" t="n">
-        <v>1</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="FY13" s="29" t="n">
         <v>2</v>
@@ -6951,35 +6953,35 @@
         <v>2</v>
       </c>
       <c r="GF13" s="31" t="n">
-        <v>11900000</v>
+        <v>34100000</v>
       </c>
       <c r="GG13" s="31" t="n">
-        <v>9004000</v>
+        <v>40614000</v>
       </c>
       <c r="GH13" s="29" t="n">
         <v>4</v>
       </c>
       <c r="GI13" s="32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="GJ13" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>Hà Tĩnh</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>81436</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Võ Anh Tuấn</t>
+          <t>Nguyễn Hùng Vương</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
@@ -6992,16 +6994,16 @@
         <v>18</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>18</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
@@ -7012,10 +7014,10 @@
         <v>4.3</v>
       </c>
       <c r="N14" s="20" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="O14" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" s="22" t="n">
         <v>1</v>
@@ -7039,10 +7041,10 @@
         <v>0.9994</v>
       </c>
       <c r="W14" s="22" t="n">
-        <v>0.9991416309012876</v>
+        <v>1</v>
       </c>
       <c r="X14" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="20" t="n">
         <v>10</v>
@@ -7054,28 +7056,28 @@
         <v>2</v>
       </c>
       <c r="AB14" s="23" t="n">
-        <v>15000000</v>
+        <v>7000000</v>
       </c>
       <c r="AC14" s="23" t="n">
-        <v>8400000</v>
+        <v>4500000</v>
       </c>
       <c r="AD14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AF14" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="20" t="n">
         <v>4.3</v>
       </c>
       <c r="AH14" s="20" t="n">
-        <v>4.275</v>
+        <v>4.57</v>
       </c>
       <c r="AI14" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ14" s="22" t="n">
         <v>1</v>
@@ -7099,7 +7101,7 @@
         <v>0.9996</v>
       </c>
       <c r="AQ14" s="22" t="n">
-        <v>0.9990398463754201</v>
+        <v>0.9988262910798122</v>
       </c>
       <c r="AR14" s="21" t="n">
         <v>0</v>
@@ -7114,25 +7116,25 @@
         <v>2</v>
       </c>
       <c r="AV14" s="23" t="n">
-        <v>13000000</v>
+        <v>6000000</v>
       </c>
       <c r="AW14" s="23" t="n">
-        <v>8550000</v>
+        <v>2100000</v>
       </c>
       <c r="AX14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AY14" s="24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AZ14" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BA14" s="20" t="n">
         <v>3.36</v>
       </c>
       <c r="BB14" s="20" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="BC14" s="21" t="n">
         <v>4</v>
@@ -7174,28 +7176,28 @@
         <v>2</v>
       </c>
       <c r="BP14" s="23" t="n">
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="BQ14" s="23" t="n">
-        <v>13570000</v>
+        <v>4460000</v>
       </c>
       <c r="BR14" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS14" s="24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BT14" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU14" s="20" t="n">
         <v>3.4</v>
       </c>
       <c r="BV14" s="20" t="n">
-        <v>3.162439529133783</v>
+        <v>3.579448347200256</v>
       </c>
       <c r="BW14" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BX14" s="22" t="n">
         <v>1</v>
@@ -7219,7 +7221,7 @@
         <v>0.9998</v>
       </c>
       <c r="CE14" s="22" t="n">
-        <v>0.9994780793319415</v>
+        <v>0.9990281827016521</v>
       </c>
       <c r="CF14" s="21" t="n">
         <v>0</v>
@@ -7234,25 +7236,25 @@
         <v>2</v>
       </c>
       <c r="CJ14" s="23" t="n">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="CK14" s="23" t="n">
-        <v>18600000</v>
+        <v>6330000</v>
       </c>
       <c r="CL14" s="21" t="n">
         <v>2</v>
       </c>
       <c r="CM14" s="24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CN14" s="21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CO14" s="20" t="n">
         <v>3.44</v>
       </c>
       <c r="CP14" s="20" t="n">
-        <v>3.677606165720625</v>
+        <v>3.488179287726036</v>
       </c>
       <c r="CQ14" s="21" t="n">
         <v>4</v>
@@ -7294,10 +7296,10 @@
         <v>2</v>
       </c>
       <c r="DD14" s="23" t="n">
-        <v>17000000</v>
+        <v>8000000</v>
       </c>
       <c r="DE14" s="23" t="n">
-        <v>11550000</v>
+        <v>5250000</v>
       </c>
       <c r="DF14" s="21" t="n">
         <v>0</v>
@@ -7312,10 +7314,10 @@
         <v>3.18</v>
       </c>
       <c r="DJ14" s="20" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="DK14" s="21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="DL14" s="22" t="n">
         <v>1</v>
@@ -7354,25 +7356,25 @@
         <v>2</v>
       </c>
       <c r="DX14" s="23" t="n">
-        <v>50000000</v>
+        <v>20000000</v>
       </c>
       <c r="DY14" s="23" t="n">
-        <v>25510000</v>
+        <v>6030000</v>
       </c>
       <c r="DZ14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="EA14" s="24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="EB14" s="21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="EC14" s="20" t="n">
         <v>3.23</v>
       </c>
       <c r="ED14" s="20" t="n">
-        <v>4.35</v>
+        <v>3.24</v>
       </c>
       <c r="EE14" s="21" t="n">
         <v>4</v>
@@ -7381,7 +7383,7 @@
         <v>0.97</v>
       </c>
       <c r="EG14" s="22" t="n">
-        <v>0.994</v>
+        <v>0.9848</v>
       </c>
       <c r="EH14" s="21" t="n">
         <v>2</v>
@@ -7390,7 +7392,7 @@
         <v>0.991</v>
       </c>
       <c r="EJ14" s="22" t="n">
-        <v>0.9995999999999999</v>
+        <v>1</v>
       </c>
       <c r="EK14" s="21" t="n">
         <v>2</v>
@@ -7399,10 +7401,10 @@
         <v>0.9998</v>
       </c>
       <c r="EM14" s="22" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="EN14" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="EO14" s="20" t="n">
         <v>10</v>
@@ -7414,34 +7416,34 @@
         <v>2</v>
       </c>
       <c r="ER14" s="23" t="n">
-        <v>37300000</v>
+        <v>10800000</v>
       </c>
       <c r="ES14" s="23" t="n">
-        <v>44220000</v>
+        <v>16610000</v>
       </c>
       <c r="ET14" s="21" t="n">
         <v>4</v>
       </c>
       <c r="EU14" s="24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="EV14" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EW14" s="20" t="n">
         <v>3.6</v>
       </c>
       <c r="EX14" s="20" t="n">
-        <v>4.49</v>
+        <v>3.57</v>
       </c>
       <c r="EY14" s="21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EZ14" s="22" t="n">
         <v>0.972</v>
       </c>
       <c r="FA14" s="22" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="FB14" s="21" t="n">
         <v>2</v>
@@ -7474,34 +7476,34 @@
         <v>2</v>
       </c>
       <c r="FL14" s="23" t="n">
-        <v>39200000</v>
+        <v>11300000</v>
       </c>
       <c r="FM14" s="23" t="n">
-        <v>46208000</v>
+        <v>21958000</v>
       </c>
       <c r="FN14" s="21" t="n">
         <v>4</v>
       </c>
       <c r="FO14" s="24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="FP14" s="21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="FQ14" s="20" t="n">
         <v>3.63</v>
       </c>
       <c r="FR14" s="20" t="n">
-        <v>4.82</v>
+        <v>3.58</v>
       </c>
       <c r="FS14" s="21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="FT14" s="22" t="n">
         <v>0.99</v>
       </c>
       <c r="FU14" s="22" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="FV14" s="21" t="n">
         <v>2</v>
@@ -7510,7 +7512,7 @@
         <v>0.993</v>
       </c>
       <c r="FX14" s="22" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="FY14" s="21" t="n">
         <v>2</v>
@@ -7528,39 +7530,39 @@
         <v>2</v>
       </c>
       <c r="GF14" s="23" t="n">
-        <v>41100000</v>
+        <v>11900000</v>
       </c>
       <c r="GG14" s="23" t="n">
-        <v>25474000</v>
+        <v>19894000</v>
       </c>
       <c r="GH14" s="21" t="n">
         <v>4</v>
       </c>
       <c r="GI14" s="24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="GJ14" s="21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Quảng Nam</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>Doãn Bá Tùng</t>
+          <t>Nguyễn Hồng Duy Linh</t>
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>18</v>
@@ -7569,16 +7571,16 @@
         <v>18</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>18</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L15" s="19" t="inlineStr">
         <is>
@@ -7589,10 +7591,10 @@
         <v>4.3</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
       <c r="O15" s="29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" s="30" t="n">
         <v>1</v>
@@ -7616,10 +7618,10 @@
         <v>0.9994</v>
       </c>
       <c r="W15" s="30" t="n">
-        <v>1</v>
+        <v>0.9987088444157521</v>
       </c>
       <c r="X15" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="28" t="n">
         <v>10</v>
@@ -7631,28 +7633,28 @@
         <v>2</v>
       </c>
       <c r="AB15" s="31" t="n">
-        <v>14000000</v>
+        <v>12000000</v>
       </c>
       <c r="AC15" s="31" t="n">
-        <v>6750000</v>
+        <v>7640000</v>
       </c>
       <c r="AD15" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="32" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AF15" s="29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG15" s="28" t="n">
         <v>4.3</v>
       </c>
       <c r="AH15" s="28" t="n">
-        <v>4.555000000000001</v>
+        <v>4.23</v>
       </c>
       <c r="AI15" s="29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="30" t="n">
         <v>1</v>
@@ -7676,10 +7678,10 @@
         <v>0.9996</v>
       </c>
       <c r="AQ15" s="30" t="n">
-        <v>0.9987915407854985</v>
+        <v>1</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS15" s="28" t="n">
         <v>10</v>
@@ -7691,25 +7693,25 @@
         <v>2</v>
       </c>
       <c r="AV15" s="31" t="n">
-        <v>12000000</v>
+        <v>11000000</v>
       </c>
       <c r="AW15" s="31" t="n">
-        <v>6150000</v>
+        <v>6450000</v>
       </c>
       <c r="AX15" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AY15" s="32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ15" s="29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA15" s="28" t="n">
         <v>3.36</v>
       </c>
       <c r="BB15" s="28" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="BC15" s="29" t="n">
         <v>4</v>
@@ -7736,10 +7738,10 @@
         <v>0.9997</v>
       </c>
       <c r="BK15" s="30" t="n">
-        <v>0.9994663820704376</v>
+        <v>1</v>
       </c>
       <c r="BL15" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM15" s="28" t="n">
         <v>10</v>
@@ -7751,25 +7753,25 @@
         <v>2</v>
       </c>
       <c r="BP15" s="31" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="BQ15" s="31" t="n">
-        <v>8700000</v>
+        <v>17689000</v>
       </c>
       <c r="BR15" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS15" s="32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BT15" s="29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU15" s="28" t="n">
         <v>3.4</v>
       </c>
       <c r="BV15" s="28" t="n">
-        <v>4.072024679485756</v>
+        <v>3.570187190011481</v>
       </c>
       <c r="BW15" s="29" t="n">
         <v>4</v>
@@ -7796,10 +7798,10 @@
         <v>0.9998</v>
       </c>
       <c r="CE15" s="30" t="n">
-        <v>0.999479979199168</v>
+        <v>1</v>
       </c>
       <c r="CF15" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG15" s="28" t="n">
         <v>10</v>
@@ -7811,28 +7813,28 @@
         <v>2</v>
       </c>
       <c r="CJ15" s="31" t="n">
-        <v>13000000</v>
+        <v>11000000</v>
       </c>
       <c r="CK15" s="31" t="n">
-        <v>13350000</v>
+        <v>16850000</v>
       </c>
       <c r="CL15" s="29" t="n">
         <v>2</v>
       </c>
       <c r="CM15" s="32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CN15" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CO15" s="28" t="n">
         <v>3.44</v>
       </c>
       <c r="CP15" s="28" t="n">
-        <v>3.64152537159249</v>
+        <v>3.316372826580352</v>
       </c>
       <c r="CQ15" s="29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CR15" s="30" t="n">
         <v>1</v>
@@ -7871,25 +7873,25 @@
         <v>2</v>
       </c>
       <c r="DD15" s="31" t="n">
-        <v>16000000</v>
+        <v>14000000</v>
       </c>
       <c r="DE15" s="31" t="n">
-        <v>12450000</v>
+        <v>31690000</v>
       </c>
       <c r="DF15" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG15" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="DH15" s="29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="DI15" s="28" t="n">
         <v>3.18</v>
       </c>
       <c r="DJ15" s="28" t="n">
-        <v>4.42</v>
+        <v>3.745</v>
       </c>
       <c r="DK15" s="29" t="n">
         <v>4</v>
@@ -7931,10 +7933,10 @@
         <v>2</v>
       </c>
       <c r="DX15" s="31" t="n">
-        <v>50000000</v>
+        <v>60000000</v>
       </c>
       <c r="DY15" s="31" t="n">
-        <v>16130000</v>
+        <v>27140000</v>
       </c>
       <c r="DZ15" s="29" t="n">
         <v>0</v>
@@ -7948,9 +7950,7 @@
       <c r="EC15" s="28" t="n">
         <v>3.23</v>
       </c>
-      <c r="ED15" s="28" t="n">
-        <v>4.54</v>
-      </c>
+      <c r="ED15" s="28" t="n"/>
       <c r="EE15" s="29" t="n">
         <v>4</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>0.97</v>
       </c>
       <c r="EG15" s="30" t="n">
-        <v>0.9843</v>
+        <v>0.983</v>
       </c>
       <c r="EH15" s="29" t="n">
         <v>2</v>
@@ -7967,7 +7967,7 @@
         <v>0.991</v>
       </c>
       <c r="EJ15" s="30" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="EK15" s="29" t="n">
         <v>2</v>
@@ -7976,10 +7976,10 @@
         <v>0.9998</v>
       </c>
       <c r="EM15" s="30" t="n">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="EN15" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EO15" s="28" t="n">
         <v>10</v>
@@ -7991,25 +7991,25 @@
         <v>2</v>
       </c>
       <c r="ER15" s="31" t="n">
-        <v>31000000</v>
+        <v>31800000</v>
       </c>
       <c r="ES15" s="31" t="n">
-        <v>25820000</v>
+        <v>24950000</v>
       </c>
       <c r="ET15" s="29" t="n">
         <v>0</v>
       </c>
       <c r="EU15" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="EV15" s="29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="EW15" s="28" t="n">
         <v>3.6</v>
       </c>
       <c r="EX15" s="28" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="EY15" s="29" t="n">
         <v>4</v>
@@ -8018,7 +8018,7 @@
         <v>0.972</v>
       </c>
       <c r="FA15" s="30" t="n">
-        <v>0.9853</v>
+        <v>0.9872</v>
       </c>
       <c r="FB15" s="29" t="n">
         <v>2</v>
@@ -8027,7 +8027,7 @@
         <v>0.992</v>
       </c>
       <c r="FD15" s="30" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
       <c r="FE15" s="29" t="n">
         <v>2</v>
@@ -8051,25 +8051,25 @@
         <v>2</v>
       </c>
       <c r="FL15" s="31" t="n">
-        <v>32500000</v>
+        <v>33400000</v>
       </c>
       <c r="FM15" s="31" t="n">
-        <v>30910000</v>
+        <v>39672000</v>
       </c>
       <c r="FN15" s="29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="FO15" s="32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="FP15" s="29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="FQ15" s="28" t="n">
         <v>3.63</v>
       </c>
       <c r="FR15" s="28" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="FS15" s="29" t="n">
         <v>4</v>
@@ -8078,7 +8078,7 @@
         <v>0.99</v>
       </c>
       <c r="FU15" s="30" t="n">
-        <v>1</v>
+        <v>0.9968</v>
       </c>
       <c r="FV15" s="29" t="n">
         <v>2</v>
@@ -8105,35 +8105,35 @@
         <v>2</v>
       </c>
       <c r="GF15" s="31" t="n">
-        <v>34100000</v>
+        <v>35000000</v>
       </c>
       <c r="GG15" s="31" t="n">
-        <v>19010000</v>
+        <v>41752000</v>
       </c>
       <c r="GH15" s="29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="GI15" s="32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="GJ15" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Đà Nẵng</t>
+          <t>Huế</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>25751</t>
+          <t>81436</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Duy Linh</t>
+          <t>Võ Anh Tuấn</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
@@ -8146,16 +8146,16 @@
         <v>18</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I16" s="17" t="n">
         <v>18</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>4.3</v>
       </c>
       <c r="N16" s="20" t="n">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="O16" s="21" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
         <v>0.9994</v>
       </c>
       <c r="W16" s="22" t="n">
-        <v>0.9987088444157521</v>
+        <v>0.9991416309012876</v>
       </c>
       <c r="X16" s="21" t="n">
         <v>0</v>
@@ -8208,10 +8208,10 @@
         <v>2</v>
       </c>
       <c r="AB16" s="23" t="n">
-        <v>12000000</v>
+        <v>15000000</v>
       </c>
       <c r="AC16" s="23" t="n">
-        <v>7640000</v>
+        <v>8400000</v>
       </c>
       <c r="AD16" s="21" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>4.3</v>
       </c>
       <c r="AH16" s="20" t="n">
-        <v>4.23</v>
+        <v>4.275</v>
       </c>
       <c r="AI16" s="21" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0.9996</v>
       </c>
       <c r="AQ16" s="22" t="n">
-        <v>1</v>
+        <v>0.9990398463754201</v>
       </c>
       <c r="AR16" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS16" s="20" t="n">
         <v>10</v>
@@ -8268,25 +8268,25 @@
         <v>2</v>
       </c>
       <c r="AV16" s="23" t="n">
-        <v>11000000</v>
+        <v>13000000</v>
       </c>
       <c r="AW16" s="23" t="n">
-        <v>6450000</v>
+        <v>8550000</v>
       </c>
       <c r="AX16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AY16" s="24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ16" s="21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA16" s="20" t="n">
         <v>3.36</v>
       </c>
       <c r="BB16" s="20" t="n">
-        <v>3.66</v>
+        <v>3.46</v>
       </c>
       <c r="BC16" s="21" t="n">
         <v>4</v>
@@ -8328,10 +8328,10 @@
         <v>2</v>
       </c>
       <c r="BP16" s="23" t="n">
-        <v>10000000</v>
+        <v>12000000</v>
       </c>
       <c r="BQ16" s="23" t="n">
-        <v>17689000</v>
+        <v>13570000</v>
       </c>
       <c r="BR16" s="21" t="n">
         <v>2</v>
@@ -8346,10 +8346,10 @@
         <v>3.4</v>
       </c>
       <c r="BV16" s="20" t="n">
-        <v>3.570187190011481</v>
+        <v>3.162439529133783</v>
       </c>
       <c r="BW16" s="21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BX16" s="22" t="n">
         <v>1</v>
@@ -8373,10 +8373,10 @@
         <v>0.9998</v>
       </c>
       <c r="CE16" s="22" t="n">
-        <v>1</v>
+        <v>0.9994780793319415</v>
       </c>
       <c r="CF16" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG16" s="20" t="n">
         <v>10</v>
@@ -8388,28 +8388,28 @@
         <v>2</v>
       </c>
       <c r="CJ16" s="23" t="n">
-        <v>11000000</v>
+        <v>14000000</v>
       </c>
       <c r="CK16" s="23" t="n">
-        <v>16850000</v>
+        <v>18600000</v>
       </c>
       <c r="CL16" s="21" t="n">
         <v>2</v>
       </c>
       <c r="CM16" s="24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CN16" s="21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CO16" s="20" t="n">
         <v>3.44</v>
       </c>
       <c r="CP16" s="20" t="n">
-        <v>3.316372826580352</v>
+        <v>3.677606165720625</v>
       </c>
       <c r="CQ16" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CR16" s="22" t="n">
         <v>1</v>
@@ -8448,25 +8448,25 @@
         <v>2</v>
       </c>
       <c r="DD16" s="23" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="DE16" s="23" t="n">
-        <v>31690000</v>
+        <v>11550000</v>
       </c>
       <c r="DF16" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG16" s="24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="DH16" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="DI16" s="20" t="n">
         <v>3.18</v>
       </c>
       <c r="DJ16" s="20" t="n">
-        <v>3.745</v>
+        <v>4</v>
       </c>
       <c r="DK16" s="21" t="n">
         <v>4</v>
@@ -8508,10 +8508,10 @@
         <v>2</v>
       </c>
       <c r="DX16" s="23" t="n">
-        <v>60000000</v>
+        <v>50000000</v>
       </c>
       <c r="DY16" s="23" t="n">
-        <v>27140000</v>
+        <v>25510000</v>
       </c>
       <c r="DZ16" s="21" t="n">
         <v>0</v>
@@ -8525,7 +8525,9 @@
       <c r="EC16" s="20" t="n">
         <v>3.23</v>
       </c>
-      <c r="ED16" s="20" t="n"/>
+      <c r="ED16" s="20" t="n">
+        <v>4.35</v>
+      </c>
       <c r="EE16" s="21" t="n">
         <v>4</v>
       </c>
@@ -8533,7 +8535,7 @@
         <v>0.97</v>
       </c>
       <c r="EG16" s="22" t="n">
-        <v>0.983</v>
+        <v>0.994</v>
       </c>
       <c r="EH16" s="21" t="n">
         <v>2</v>
@@ -8542,7 +8544,7 @@
         <v>0.991</v>
       </c>
       <c r="EJ16" s="22" t="n">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="EK16" s="21" t="n">
         <v>2</v>
@@ -8551,7 +8553,7 @@
         <v>0.9998</v>
       </c>
       <c r="EM16" s="22" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="EN16" s="21" t="n">
         <v>0</v>
@@ -8566,25 +8568,25 @@
         <v>2</v>
       </c>
       <c r="ER16" s="23" t="n">
-        <v>31800000</v>
+        <v>37300000</v>
       </c>
       <c r="ES16" s="23" t="n">
-        <v>24950000</v>
+        <v>44220000</v>
       </c>
       <c r="ET16" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="EU16" s="24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="EV16" s="21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="EW16" s="20" t="n">
         <v>3.6</v>
       </c>
       <c r="EX16" s="20" t="n">
-        <v>4.42</v>
+        <v>4.49</v>
       </c>
       <c r="EY16" s="21" t="n">
         <v>4</v>
@@ -8593,7 +8595,7 @@
         <v>0.972</v>
       </c>
       <c r="FA16" s="22" t="n">
-        <v>0.9872</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="FB16" s="21" t="n">
         <v>2</v>
@@ -8602,7 +8604,7 @@
         <v>0.992</v>
       </c>
       <c r="FD16" s="22" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="FE16" s="21" t="n">
         <v>2</v>
@@ -8626,10 +8628,10 @@
         <v>2</v>
       </c>
       <c r="FL16" s="23" t="n">
-        <v>33400000</v>
+        <v>39200000</v>
       </c>
       <c r="FM16" s="23" t="n">
-        <v>39672000</v>
+        <v>46208000</v>
       </c>
       <c r="FN16" s="21" t="n">
         <v>4</v>
@@ -8644,7 +8646,7 @@
         <v>3.63</v>
       </c>
       <c r="FR16" s="20" t="n">
-        <v>4.49</v>
+        <v>4.82</v>
       </c>
       <c r="FS16" s="21" t="n">
         <v>4</v>
@@ -8653,7 +8655,7 @@
         <v>0.99</v>
       </c>
       <c r="FU16" s="22" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9992</v>
       </c>
       <c r="FV16" s="21" t="n">
         <v>2</v>
@@ -8662,7 +8664,7 @@
         <v>0.993</v>
       </c>
       <c r="FX16" s="22" t="n">
-        <v>1</v>
+        <v>0.9945999999999999</v>
       </c>
       <c r="FY16" s="21" t="n">
         <v>2</v>
@@ -8680,19 +8682,19 @@
         <v>2</v>
       </c>
       <c r="GF16" s="23" t="n">
-        <v>35000000</v>
+        <v>41100000</v>
       </c>
       <c r="GG16" s="23" t="n">
-        <v>18260000</v>
+        <v>46584000</v>
       </c>
       <c r="GH16" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="GI16" s="24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="GJ16" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -9228,7 +9230,7 @@
         <v>0.99</v>
       </c>
       <c r="FU17" s="30" t="n">
-        <v>0.9961</v>
+        <v>0.9979</v>
       </c>
       <c r="FV17" s="29" t="n">
         <v>2</v>
@@ -9237,7 +9239,7 @@
         <v>0.993</v>
       </c>
       <c r="FX17" s="30" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="FY17" s="29" t="n">
         <v>2</v>
@@ -9258,7 +9260,7 @@
         <v>20100000</v>
       </c>
       <c r="GG17" s="31" t="n">
-        <v>4544000</v>
+        <v>16754000</v>
       </c>
       <c r="GH17" s="29" t="n">
         <v>0</v>
@@ -9796,7 +9798,7 @@
         <v>3.63</v>
       </c>
       <c r="FR18" s="20" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="FS18" s="21" t="n">
         <v>0</v>
@@ -9805,7 +9807,7 @@
         <v>0.99</v>
       </c>
       <c r="FU18" s="22" t="n">
-        <v>0.995</v>
+        <v>0.9947</v>
       </c>
       <c r="FV18" s="21" t="n">
         <v>2</v>
@@ -9835,7 +9837,7 @@
         <v>13400000</v>
       </c>
       <c r="GG18" s="23" t="n">
-        <v>10540000</v>
+        <v>17164000</v>
       </c>
       <c r="GH18" s="21" t="n">
         <v>4</v>
@@ -9844,7 +9846,7 @@
         <v>10</v>
       </c>
       <c r="GJ18" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10274,7 +10276,7 @@
       <c r="DO2" s="8" t="n"/>
       <c r="DP2" s="35" t="inlineStr">
         <is>
-          <t>THÁNG 9 · tới 22/09</t>
+          <t>THÁNG 9</t>
         </is>
       </c>
       <c r="DQ2" s="36" t="n"/>
@@ -11260,12 +11262,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>Phan Văn Tuấn</t>
+          <t>Nguyễn Hoàng Huy</t>
         </is>
       </c>
       <c r="G6" s="39" t="inlineStr">
@@ -11288,7 +11290,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>186178657</v>
+        <v>98159579</v>
       </c>
       <c r="M6" s="41" t="n">
         <v>54</v>
@@ -11314,7 +11316,7 @@
         <v>0.4676</v>
       </c>
       <c r="T6" s="43" t="n">
-        <v>0.7239</v>
+        <v>0.9429000000000001</v>
       </c>
       <c r="U6" s="21" t="n">
         <v>2</v>
@@ -11329,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="Y6" s="23" t="n">
-        <v>29639985</v>
+        <v>11619185</v>
       </c>
       <c r="Z6" s="24" t="n">
         <v>6</v>
@@ -11355,7 +11357,7 @@
         <v>0.3569</v>
       </c>
       <c r="AG6" s="43" t="n">
-        <v>0.6770999999999999</v>
+        <v>0.8667</v>
       </c>
       <c r="AH6" s="21" t="n">
         <v>2</v>
@@ -11370,7 +11372,7 @@
         <v>2</v>
       </c>
       <c r="AL6" s="23" t="n">
-        <v>17691833</v>
+        <v>8457917</v>
       </c>
       <c r="AM6" s="24" t="n">
         <v>6</v>
@@ -11396,7 +11398,7 @@
         <v>0.449</v>
       </c>
       <c r="AT6" s="43" t="n">
-        <v>0.6577</v>
+        <v>0.8802</v>
       </c>
       <c r="AU6" s="21" t="n">
         <v>2</v>
@@ -11411,7 +11413,7 @@
         <v>2</v>
       </c>
       <c r="AY6" s="23" t="n">
-        <v>29991000</v>
+        <v>12298000</v>
       </c>
       <c r="AZ6" s="24" t="n">
         <v>6</v>
@@ -11437,7 +11439,7 @@
         <v>0.4045</v>
       </c>
       <c r="BG6" s="43" t="n">
-        <v>0.662</v>
+        <v>0.6419</v>
       </c>
       <c r="BH6" s="21" t="n">
         <v>2</v>
@@ -11452,7 +11454,7 @@
         <v>2</v>
       </c>
       <c r="BL6" s="23" t="n">
-        <v>25082846</v>
+        <v>12811846</v>
       </c>
       <c r="BM6" s="24" t="n">
         <v>6</v>
@@ -11478,7 +11480,7 @@
         <v>0.4486</v>
       </c>
       <c r="BT6" s="43" t="n">
-        <v>0.7254999999999999</v>
+        <v>0.6803</v>
       </c>
       <c r="BU6" s="21" t="n">
         <v>2</v>
@@ -11493,7 +11495,7 @@
         <v>2</v>
       </c>
       <c r="BY6" s="23" t="n">
-        <v>26569923</v>
+        <v>22306846</v>
       </c>
       <c r="BZ6" s="24" t="n">
         <v>6</v>
@@ -11519,7 +11521,7 @@
         <v>0.3201</v>
       </c>
       <c r="CG6" s="43" t="n">
-        <v>0.7492</v>
+        <v>0.5047999999999999</v>
       </c>
       <c r="CH6" s="21" t="n">
         <v>2</v>
@@ -11534,7 +11536,7 @@
         <v>2</v>
       </c>
       <c r="CL6" s="23" t="n">
-        <v>27673700</v>
+        <v>16250000</v>
       </c>
       <c r="CM6" s="24" t="n">
         <v>6</v>
@@ -11560,7 +11562,7 @@
         <v>0.4752</v>
       </c>
       <c r="CT6" s="43" t="n">
-        <v>0.769</v>
+        <v>0.6513</v>
       </c>
       <c r="CU6" s="21" t="n">
         <v>2</v>
@@ -11575,7 +11577,7 @@
         <v>2</v>
       </c>
       <c r="CY6" s="23" t="n">
-        <v>29529370</v>
+        <v>14415785</v>
       </c>
       <c r="CZ6" s="24" t="n">
         <v>6</v>
@@ -11601,7 +11603,7 @@
         <v>0.4838</v>
       </c>
       <c r="DG6" s="43" t="n">
-        <v>0.7857</v>
+        <v>0.5588</v>
       </c>
       <c r="DH6" s="21" t="n">
         <v>2</v>
@@ -11637,10 +11639,10 @@
         <v>2</v>
       </c>
       <c r="DS6" s="43" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT6" s="43" t="n">
-        <v>0.798</v>
+        <v>0.5063</v>
       </c>
       <c r="DU6" s="21" t="n">
         <v>2</v>
@@ -11685,12 +11687,12 @@
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>80856</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="F7" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Hoàng Huy</t>
+          <t>Phan Văn Tuấn</t>
         </is>
       </c>
       <c r="G7" s="45" t="inlineStr">
@@ -11704,7 +11706,7 @@
         </is>
       </c>
       <c r="I7" s="17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J7" s="17" t="n">
         <v>18</v>
@@ -11713,13 +11715,13 @@
         <v>18</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>98159579</v>
+        <v>186178657</v>
       </c>
       <c r="M7" s="41" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N7" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
@@ -11739,7 +11741,7 @@
         <v>0.4676</v>
       </c>
       <c r="T7" s="46" t="n">
-        <v>0.9429000000000001</v>
+        <v>0.7239</v>
       </c>
       <c r="U7" s="29" t="n">
         <v>2</v>
@@ -11754,7 +11756,7 @@
         <v>2</v>
       </c>
       <c r="Y7" s="31" t="n">
-        <v>11619185</v>
+        <v>29639985</v>
       </c>
       <c r="Z7" s="32" t="n">
         <v>6</v>
@@ -11780,7 +11782,7 @@
         <v>0.3569</v>
       </c>
       <c r="AG7" s="46" t="n">
-        <v>0.8667</v>
+        <v>0.6770999999999999</v>
       </c>
       <c r="AH7" s="29" t="n">
         <v>2</v>
@@ -11795,7 +11797,7 @@
         <v>2</v>
       </c>
       <c r="AL7" s="31" t="n">
-        <v>8457917</v>
+        <v>17691833</v>
       </c>
       <c r="AM7" s="32" t="n">
         <v>6</v>
@@ -11821,7 +11823,7 @@
         <v>0.449</v>
       </c>
       <c r="AT7" s="46" t="n">
-        <v>0.8802</v>
+        <v>0.6577</v>
       </c>
       <c r="AU7" s="29" t="n">
         <v>2</v>
@@ -11836,7 +11838,7 @@
         <v>2</v>
       </c>
       <c r="AY7" s="31" t="n">
-        <v>12298000</v>
+        <v>29991000</v>
       </c>
       <c r="AZ7" s="32" t="n">
         <v>6</v>
@@ -11862,7 +11864,7 @@
         <v>0.4045</v>
       </c>
       <c r="BG7" s="46" t="n">
-        <v>0.6419</v>
+        <v>0.662</v>
       </c>
       <c r="BH7" s="29" t="n">
         <v>2</v>
@@ -11877,7 +11879,7 @@
         <v>2</v>
       </c>
       <c r="BL7" s="31" t="n">
-        <v>12811846</v>
+        <v>25082846</v>
       </c>
       <c r="BM7" s="32" t="n">
         <v>6</v>
@@ -11903,7 +11905,7 @@
         <v>0.4486</v>
       </c>
       <c r="BT7" s="46" t="n">
-        <v>0.6803</v>
+        <v>0.7254999999999999</v>
       </c>
       <c r="BU7" s="29" t="n">
         <v>2</v>
@@ -11918,7 +11920,7 @@
         <v>2</v>
       </c>
       <c r="BY7" s="31" t="n">
-        <v>22306846</v>
+        <v>26569923</v>
       </c>
       <c r="BZ7" s="32" t="n">
         <v>6</v>
@@ -11944,7 +11946,7 @@
         <v>0.3201</v>
       </c>
       <c r="CG7" s="46" t="n">
-        <v>0.5047999999999999</v>
+        <v>0.7492</v>
       </c>
       <c r="CH7" s="29" t="n">
         <v>2</v>
@@ -11959,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="CL7" s="31" t="n">
-        <v>16250000</v>
+        <v>27673700</v>
       </c>
       <c r="CM7" s="32" t="n">
         <v>6</v>
@@ -11985,7 +11987,7 @@
         <v>0.4752</v>
       </c>
       <c r="CT7" s="46" t="n">
-        <v>0.6513</v>
+        <v>0.769</v>
       </c>
       <c r="CU7" s="29" t="n">
         <v>2</v>
@@ -12000,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="CY7" s="31" t="n">
-        <v>14415785</v>
+        <v>29529370</v>
       </c>
       <c r="CZ7" s="32" t="n">
         <v>6</v>
@@ -12026,7 +12028,7 @@
         <v>0.4838</v>
       </c>
       <c r="DG7" s="46" t="n">
-        <v>0.5588</v>
+        <v>0.7857</v>
       </c>
       <c r="DH7" s="29" t="n">
         <v>2</v>
@@ -12056,16 +12058,16 @@
         <v>0</v>
       </c>
       <c r="DQ7" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR7" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS7" s="46" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT7" s="46" t="n">
-        <v>0.5104</v>
+        <v>0.7441</v>
       </c>
       <c r="DU7" s="29" t="n">
         <v>2</v>
@@ -12081,16 +12083,12 @@
       </c>
       <c r="DY7" s="31" t="n"/>
       <c r="DZ7" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA7" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB7" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="EB7" s="45" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="14" t="inlineStr">
@@ -12455,10 +12453,10 @@
         <v>2</v>
       </c>
       <c r="DS8" s="43" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT8" s="43" t="n">
-        <v>0.5641</v>
+        <v>0.5802</v>
       </c>
       <c r="DU8" s="21" t="n">
         <v>2</v>
@@ -12850,10 +12848,10 @@
         <v>2</v>
       </c>
       <c r="DS9" s="46" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT9" s="46" t="n">
-        <v>0.5342</v>
+        <v>0.529</v>
       </c>
       <c r="DU9" s="29" t="n">
         <v>2</v>
@@ -13247,10 +13245,10 @@
         <v>2</v>
       </c>
       <c r="DS10" s="43" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT10" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.4813</v>
       </c>
       <c r="DU10" s="21" t="n">
         <v>2</v>
@@ -13295,12 +13293,12 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>86190</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Luân</t>
+          <t>Quản Minh Vân</t>
         </is>
       </c>
       <c r="G11" s="45" t="inlineStr">
@@ -13314,16 +13312,16 @@
         </is>
       </c>
       <c r="I11" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>134069510</v>
+        <v>86916491</v>
       </c>
       <c r="M11" s="41" t="n">
         <v>40</v>
@@ -13336,16 +13334,16 @@
         <v>0</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="46" t="n">
         <v>0.4676</v>
       </c>
       <c r="T11" s="46" t="n">
-        <v>0.3296</v>
+        <v>0.1667</v>
       </c>
       <c r="U11" s="29" t="n">
         <v>0</v>
@@ -13360,13 +13358,13 @@
         <v>2</v>
       </c>
       <c r="Y11" s="31" t="n">
-        <v>28390370</v>
+        <v>9024185</v>
       </c>
       <c r="Z11" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB11" s="45" t="n"/>
       <c r="AC11" s="29" t="n">
@@ -13382,7 +13380,7 @@
         <v>0.3569</v>
       </c>
       <c r="AG11" s="46" t="n">
-        <v>0.1585</v>
+        <v>0.1308</v>
       </c>
       <c r="AH11" s="29" t="n">
         <v>0</v>
@@ -13397,7 +13395,7 @@
         <v>2</v>
       </c>
       <c r="AL11" s="31" t="n">
-        <v>12393417</v>
+        <v>9573583</v>
       </c>
       <c r="AM11" s="32" t="n">
         <v>4</v>
@@ -13419,7 +13417,7 @@
         <v>0.449</v>
       </c>
       <c r="AT11" s="46" t="n">
-        <v>0.133</v>
+        <v>0.3333</v>
       </c>
       <c r="AU11" s="29" t="n">
         <v>0</v>
@@ -13434,7 +13432,7 @@
         <v>2</v>
       </c>
       <c r="AY11" s="31" t="n">
-        <v>15112846</v>
+        <v>11219846</v>
       </c>
       <c r="AZ11" s="32" t="n">
         <v>4</v>
@@ -13456,7 +13454,7 @@
         <v>0.4045</v>
       </c>
       <c r="BG11" s="46" t="n">
-        <v>0.1067</v>
+        <v>0.3431</v>
       </c>
       <c r="BH11" s="29" t="n">
         <v>0</v>
@@ -13471,7 +13469,7 @@
         <v>2</v>
       </c>
       <c r="BL11" s="31" t="n">
-        <v>15869846</v>
+        <v>11949846</v>
       </c>
       <c r="BM11" s="32" t="n">
         <v>4</v>
@@ -13493,7 +13491,7 @@
         <v>0.4486</v>
       </c>
       <c r="BT11" s="46" t="n">
-        <v>0.3158</v>
+        <v>0.3451</v>
       </c>
       <c r="BU11" s="29" t="n">
         <v>0</v>
@@ -13508,7 +13506,7 @@
         <v>2</v>
       </c>
       <c r="BY11" s="31" t="n">
-        <v>22133846</v>
+        <v>16655923</v>
       </c>
       <c r="BZ11" s="32" t="n">
         <v>4</v>
@@ -13530,7 +13528,7 @@
         <v>0.3201</v>
       </c>
       <c r="CG11" s="46" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2762</v>
       </c>
       <c r="CH11" s="29" t="n">
         <v>0</v>
@@ -13545,7 +13543,7 @@
         <v>2</v>
       </c>
       <c r="CL11" s="31" t="n">
-        <v>20787000</v>
+        <v>15297923</v>
       </c>
       <c r="CM11" s="32" t="n">
         <v>4</v>
@@ -13567,10 +13565,10 @@
         <v>0.4752</v>
       </c>
       <c r="CT11" s="46" t="n">
-        <v>0.5326</v>
+        <v>0.4539</v>
       </c>
       <c r="CU11" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV11" s="29" t="n">
         <v>0</v>
@@ -13582,19 +13580,15 @@
         <v>2</v>
       </c>
       <c r="CY11" s="31" t="n">
-        <v>19382185</v>
+        <v>13195185</v>
       </c>
       <c r="CZ11" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="DA11" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB11" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="DB11" s="45" t="n"/>
       <c r="DC11" s="29" t="n">
         <v>0</v>
       </c>
@@ -13608,7 +13602,7 @@
         <v>0.4838</v>
       </c>
       <c r="DG11" s="46" t="n">
-        <v>0.5877</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="DH11" s="29" t="n">
         <v>2</v>
@@ -13644,10 +13638,10 @@
         <v>2</v>
       </c>
       <c r="DS11" s="46" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT11" s="46" t="n">
-        <v>0.475</v>
+        <v>0.4795</v>
       </c>
       <c r="DU11" s="29" t="n">
         <v>2</v>
@@ -13692,12 +13686,12 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>86190</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>Quản Minh Vân</t>
+          <t>Nguyễn Thành Luân</t>
         </is>
       </c>
       <c r="G12" s="39" t="inlineStr">
@@ -13711,16 +13705,16 @@
         </is>
       </c>
       <c r="I12" s="17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>86916491</v>
+        <v>134069510</v>
       </c>
       <c r="M12" s="41" t="n">
         <v>38</v>
@@ -13733,16 +13727,16 @@
         <v>0</v>
       </c>
       <c r="Q12" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" s="43" t="n">
         <v>0.4676</v>
       </c>
       <c r="T12" s="43" t="n">
-        <v>0.1667</v>
+        <v>0.3296</v>
       </c>
       <c r="U12" s="21" t="n">
         <v>0</v>
@@ -13757,13 +13751,13 @@
         <v>2</v>
       </c>
       <c r="Y12" s="23" t="n">
-        <v>9024185</v>
+        <v>28390370</v>
       </c>
       <c r="Z12" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA12" s="21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB12" s="39" t="n"/>
       <c r="AC12" s="21" t="n">
@@ -13779,7 +13773,7 @@
         <v>0.3569</v>
       </c>
       <c r="AG12" s="43" t="n">
-        <v>0.1308</v>
+        <v>0.1585</v>
       </c>
       <c r="AH12" s="21" t="n">
         <v>0</v>
@@ -13794,7 +13788,7 @@
         <v>2</v>
       </c>
       <c r="AL12" s="23" t="n">
-        <v>9573583</v>
+        <v>12393417</v>
       </c>
       <c r="AM12" s="24" t="n">
         <v>4</v>
@@ -13816,7 +13810,7 @@
         <v>0.449</v>
       </c>
       <c r="AT12" s="43" t="n">
-        <v>0.3333</v>
+        <v>0.133</v>
       </c>
       <c r="AU12" s="21" t="n">
         <v>0</v>
@@ -13831,7 +13825,7 @@
         <v>2</v>
       </c>
       <c r="AY12" s="23" t="n">
-        <v>11219846</v>
+        <v>15112846</v>
       </c>
       <c r="AZ12" s="24" t="n">
         <v>4</v>
@@ -13853,7 +13847,7 @@
         <v>0.4045</v>
       </c>
       <c r="BG12" s="43" t="n">
-        <v>0.3431</v>
+        <v>0.1067</v>
       </c>
       <c r="BH12" s="21" t="n">
         <v>0</v>
@@ -13868,7 +13862,7 @@
         <v>2</v>
       </c>
       <c r="BL12" s="23" t="n">
-        <v>11949846</v>
+        <v>15869846</v>
       </c>
       <c r="BM12" s="24" t="n">
         <v>4</v>
@@ -13890,7 +13884,7 @@
         <v>0.4486</v>
       </c>
       <c r="BT12" s="43" t="n">
-        <v>0.3451</v>
+        <v>0.3158</v>
       </c>
       <c r="BU12" s="21" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>2</v>
       </c>
       <c r="BY12" s="23" t="n">
-        <v>16655923</v>
+        <v>22133846</v>
       </c>
       <c r="BZ12" s="24" t="n">
         <v>4</v>
@@ -13927,7 +13921,7 @@
         <v>0.3201</v>
       </c>
       <c r="CG12" s="43" t="n">
-        <v>0.2762</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="CH12" s="21" t="n">
         <v>0</v>
@@ -13942,7 +13936,7 @@
         <v>2</v>
       </c>
       <c r="CL12" s="23" t="n">
-        <v>15297923</v>
+        <v>20787000</v>
       </c>
       <c r="CM12" s="24" t="n">
         <v>4</v>
@@ -13964,10 +13958,10 @@
         <v>0.4752</v>
       </c>
       <c r="CT12" s="43" t="n">
-        <v>0.4539</v>
+        <v>0.5326</v>
       </c>
       <c r="CU12" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV12" s="21" t="n">
         <v>0</v>
@@ -13979,15 +13973,19 @@
         <v>2</v>
       </c>
       <c r="CY12" s="23" t="n">
-        <v>13195185</v>
+        <v>19382185</v>
       </c>
       <c r="CZ12" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DA12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="DB12" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="DB12" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="DC12" s="21" t="n">
         <v>0</v>
       </c>
@@ -14001,7 +13999,7 @@
         <v>0.4838</v>
       </c>
       <c r="DG12" s="43" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5877</v>
       </c>
       <c r="DH12" s="21" t="n">
         <v>2</v>
@@ -14037,10 +14035,10 @@
         <v>2</v>
       </c>
       <c r="DS12" s="43" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT12" s="43" t="n">
-        <v>0.4434</v>
+        <v>0.4118</v>
       </c>
       <c r="DU12" s="21" t="n">
         <v>0</v>
@@ -14059,7 +14057,7 @@
         <v>4</v>
       </c>
       <c r="EA12" s="21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="EB12" s="39" t="n"/>
     </row>
@@ -14420,10 +14418,10 @@
         <v>2</v>
       </c>
       <c r="DS13" s="46" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT13" s="46" t="n">
-        <v>0.1525</v>
+        <v>0.2996</v>
       </c>
       <c r="DU13" s="29" t="n">
         <v>0</v>
@@ -14442,7 +14440,7 @@
         <v>4</v>
       </c>
       <c r="EA13" s="29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="EB13" s="45" t="n"/>
     </row>
@@ -14583,10 +14581,10 @@
         <v>2</v>
       </c>
       <c r="DS14" s="43" t="n">
-        <v>0.4544</v>
+        <v>0.4656</v>
       </c>
       <c r="DT14" s="43" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1587</v>
       </c>
       <c r="DU14" s="21" t="n">
         <v>0</v>
@@ -14605,7 +14603,7 @@
         <v>4</v>
       </c>
       <c r="EA14" s="21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="EB14" s="39" t="n"/>
     </row>
@@ -14988,10 +14986,10 @@
         <v>2</v>
       </c>
       <c r="DS15" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT15" s="46" t="n">
-        <v>0.7639</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="DU15" s="29" t="n">
         <v>2</v>
@@ -15409,7 +15407,7 @@
         <v>0</v>
       </c>
       <c r="DS16" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT16" s="43" t="n">
         <v>0.5217000000000001</v>
@@ -15826,7 +15824,7 @@
         <v>2</v>
       </c>
       <c r="DS17" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT17" s="46" t="n">
         <v>0.3824</v>
@@ -16229,10 +16227,10 @@
         <v>2</v>
       </c>
       <c r="DS18" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT18" s="43" t="n">
-        <v>0.6125</v>
+        <v>0.5748</v>
       </c>
       <c r="DU18" s="21" t="n">
         <v>2</v>
@@ -16638,10 +16636,10 @@
         <v>2</v>
       </c>
       <c r="DS19" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT19" s="46" t="n">
-        <v>0.5476</v>
+        <v>0.5419</v>
       </c>
       <c r="DU19" s="29" t="n">
         <v>2</v>
@@ -17047,10 +17045,10 @@
         <v>2</v>
       </c>
       <c r="DS20" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT20" s="43" t="n">
-        <v>0.2763</v>
+        <v>0.3056</v>
       </c>
       <c r="DU20" s="21" t="n">
         <v>0</v>
@@ -17432,10 +17430,10 @@
         <v>2</v>
       </c>
       <c r="DS21" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT21" s="46" t="n">
-        <v>0.3579</v>
+        <v>0.3988</v>
       </c>
       <c r="DU21" s="29" t="n">
         <v>0</v>
@@ -17813,10 +17811,10 @@
         <v>2</v>
       </c>
       <c r="DS22" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT22" s="43" t="n">
-        <v>0.2234</v>
+        <v>0.2368</v>
       </c>
       <c r="DU22" s="21" t="n">
         <v>0</v>
@@ -18198,10 +18196,10 @@
         <v>2</v>
       </c>
       <c r="DS23" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT23" s="46" t="n">
-        <v>0.2283</v>
+        <v>0.239</v>
       </c>
       <c r="DU23" s="29" t="n">
         <v>0</v>
@@ -18585,10 +18583,10 @@
         <v>2</v>
       </c>
       <c r="DS24" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT24" s="43" t="n">
-        <v>0.0357</v>
+        <v>0.128</v>
       </c>
       <c r="DU24" s="21" t="n">
         <v>0</v>
@@ -18978,10 +18976,10 @@
         <v>2</v>
       </c>
       <c r="DS25" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT25" s="46" t="n">
-        <v>0.6412</v>
+        <v>0.681</v>
       </c>
       <c r="DU25" s="29" t="n">
         <v>2</v>
@@ -19365,10 +19363,10 @@
         <v>2</v>
       </c>
       <c r="DS26" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT26" s="43" t="n">
-        <v>0.2167</v>
+        <v>0.3191</v>
       </c>
       <c r="DU26" s="21" t="n">
         <v>0</v>
@@ -19744,10 +19742,10 @@
         <v>2</v>
       </c>
       <c r="DS27" s="46" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT27" s="46" t="n">
-        <v>0.098</v>
+        <v>0.1039</v>
       </c>
       <c r="DU27" s="29" t="n">
         <v>0</v>
@@ -19948,10 +19946,10 @@
         <v>2</v>
       </c>
       <c r="DS28" s="43" t="n">
-        <v>0.3954</v>
+        <v>0.4162</v>
       </c>
       <c r="DT28" s="43" t="n">
-        <v>0.6296</v>
+        <v>0.6744</v>
       </c>
       <c r="DU28" s="21" t="n">
         <v>2</v>
@@ -20361,10 +20359,10 @@
         <v>2</v>
       </c>
       <c r="DS29" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT29" s="46" t="n">
-        <v>0.4059</v>
+        <v>0.3586</v>
       </c>
       <c r="DU29" s="29" t="n">
         <v>2</v>
@@ -20778,10 +20776,10 @@
         <v>2</v>
       </c>
       <c r="DS30" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT30" s="43" t="n">
-        <v>0.3137</v>
+        <v>0.3697</v>
       </c>
       <c r="DU30" s="21" t="n">
         <v>2</v>
@@ -21193,10 +21191,10 @@
         <v>2</v>
       </c>
       <c r="DS31" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT31" s="46" t="n">
-        <v>0.3984</v>
+        <v>0.4247</v>
       </c>
       <c r="DU31" s="29" t="n">
         <v>2</v>
@@ -21604,10 +21602,10 @@
         <v>2</v>
       </c>
       <c r="DS32" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT32" s="43" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="DU32" s="21" t="n">
         <v>2</v>
@@ -22001,10 +21999,10 @@
         <v>2</v>
       </c>
       <c r="DS33" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT33" s="46" t="n">
-        <v>0.3614</v>
+        <v>0.3551</v>
       </c>
       <c r="DU33" s="29" t="n">
         <v>2</v>
@@ -22396,10 +22394,10 @@
         <v>2</v>
       </c>
       <c r="DS34" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT34" s="43" t="n">
-        <v>0.1471</v>
+        <v>0.2069</v>
       </c>
       <c r="DU34" s="21" t="n">
         <v>0</v>
@@ -22785,10 +22783,10 @@
         <v>2</v>
       </c>
       <c r="DS35" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT35" s="46" t="n">
-        <v>0.3594</v>
+        <v>0.4038</v>
       </c>
       <c r="DU35" s="29" t="n">
         <v>2</v>
@@ -23176,10 +23174,10 @@
         <v>2</v>
       </c>
       <c r="DS36" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT36" s="43" t="n">
-        <v>0.3396</v>
+        <v>0.4112</v>
       </c>
       <c r="DU36" s="21" t="n">
         <v>2</v>
@@ -23569,10 +23567,10 @@
         <v>2</v>
       </c>
       <c r="DS37" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT37" s="46" t="n">
-        <v>0.2264</v>
+        <v>0.2819</v>
       </c>
       <c r="DU37" s="29" t="n">
         <v>0</v>
@@ -23954,10 +23952,10 @@
         <v>2</v>
       </c>
       <c r="DS38" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT38" s="43" t="n">
-        <v>0.3977</v>
+        <v>0.4361</v>
       </c>
       <c r="DU38" s="21" t="n">
         <v>2</v>
@@ -24343,10 +24341,10 @@
         <v>2</v>
       </c>
       <c r="DS39" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT39" s="46" t="n">
-        <v>0.0795</v>
+        <v>0.1583</v>
       </c>
       <c r="DU39" s="29" t="n">
         <v>0</v>
@@ -24432,10 +24430,10 @@
         <v>2</v>
       </c>
       <c r="DS40" s="43" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT40" s="43" t="n">
-        <v>0.0392</v>
+        <v>0.1348</v>
       </c>
       <c r="DU40" s="21" t="n">
         <v>0</v>
@@ -24521,10 +24519,10 @@
         <v>2</v>
       </c>
       <c r="DS41" s="46" t="n">
-        <v>0.2836</v>
+        <v>0.3248</v>
       </c>
       <c r="DT41" s="46" t="n">
-        <v>0.0588</v>
+        <v>0.1333</v>
       </c>
       <c r="DU41" s="29" t="n">
         <v>0</v>
@@ -24942,10 +24940,10 @@
         <v>2</v>
       </c>
       <c r="DS42" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT42" s="43" t="n">
-        <v>0.578</v>
+        <v>0.575</v>
       </c>
       <c r="DU42" s="21" t="n">
         <v>2</v>
@@ -24990,12 +24988,12 @@
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>171007</t>
+          <t>262826</t>
         </is>
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Trọng Tấn</t>
+          <t>Mai Ngọc Lợi</t>
         </is>
       </c>
       <c r="G43" s="45" t="inlineStr">
@@ -25018,7 +25016,7 @@
         <v>18</v>
       </c>
       <c r="L43" s="40" t="n">
-        <v>77482493</v>
+        <v>97184777</v>
       </c>
       <c r="M43" s="41" t="n">
         <v>52</v>
@@ -25041,10 +25039,10 @@
         <v>2</v>
       </c>
       <c r="S43" s="46" t="n">
-        <v>0.2494</v>
+        <v>0.2387</v>
       </c>
       <c r="T43" s="46" t="n">
-        <v>0.0207</v>
+        <v>0.2203</v>
       </c>
       <c r="U43" s="29" t="n">
         <v>0</v>
@@ -25059,7 +25057,7 @@
         <v>2</v>
       </c>
       <c r="Y43" s="31" t="n">
-        <v>9797000</v>
+        <v>11591000</v>
       </c>
       <c r="Z43" s="32" t="n">
         <v>4</v>
@@ -25078,10 +25076,10 @@
         <v>2</v>
       </c>
       <c r="AF43" s="46" t="n">
-        <v>0.2092</v>
+        <v>0.2272</v>
       </c>
       <c r="AG43" s="46" t="n">
-        <v>0.385</v>
+        <v>0.3832</v>
       </c>
       <c r="AH43" s="29" t="n">
         <v>2</v>
@@ -25096,7 +25094,7 @@
         <v>2</v>
       </c>
       <c r="AL43" s="31" t="n">
-        <v>13171000</v>
+        <v>11174000</v>
       </c>
       <c r="AM43" s="32" t="n">
         <v>6</v>
@@ -25119,10 +25117,10 @@
         <v>2</v>
       </c>
       <c r="AS43" s="46" t="n">
-        <v>0.3277</v>
+        <v>0.4095</v>
       </c>
       <c r="AT43" s="46" t="n">
-        <v>0.6142</v>
+        <v>0.5764</v>
       </c>
       <c r="AU43" s="29" t="n">
         <v>2</v>
@@ -25137,7 +25135,7 @@
         <v>2</v>
       </c>
       <c r="AY43" s="31" t="n">
-        <v>10920000</v>
+        <v>14891000</v>
       </c>
       <c r="AZ43" s="32" t="n">
         <v>6</v>
@@ -25145,7 +25143,11 @@
       <c r="BA43" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="BB43" s="45" t="n"/>
+      <c r="BB43" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="BC43" s="29" t="n">
         <v>0</v>
       </c>
@@ -25156,10 +25158,10 @@
         <v>2</v>
       </c>
       <c r="BF43" s="46" t="n">
-        <v>0.4095</v>
+        <v>0.412</v>
       </c>
       <c r="BG43" s="46" t="n">
-        <v>0.5962</v>
+        <v>0.5371</v>
       </c>
       <c r="BH43" s="29" t="n">
         <v>2</v>
@@ -25174,7 +25176,7 @@
         <v>2</v>
       </c>
       <c r="BL43" s="31" t="n">
-        <v>9087462</v>
+        <v>15508846</v>
       </c>
       <c r="BM43" s="32" t="n">
         <v>6</v>
@@ -25182,7 +25184,11 @@
       <c r="BN43" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="BO43" s="45" t="n"/>
+      <c r="BO43" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="BP43" s="29" t="n">
         <v>0</v>
       </c>
@@ -25193,10 +25199,10 @@
         <v>2</v>
       </c>
       <c r="BS43" s="46" t="n">
-        <v>0.3564</v>
+        <v>0.431</v>
       </c>
       <c r="BT43" s="46" t="n">
-        <v>0.5211</v>
+        <v>0.4977</v>
       </c>
       <c r="BU43" s="29" t="n">
         <v>2</v>
@@ -25211,7 +25217,7 @@
         <v>2</v>
       </c>
       <c r="BY43" s="31" t="n">
-        <v>14424231</v>
+        <v>20384231</v>
       </c>
       <c r="BZ43" s="32" t="n">
         <v>6</v>
@@ -25219,7 +25225,11 @@
       <c r="CA43" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="CB43" s="45" t="n"/>
+      <c r="CB43" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="CC43" s="29" t="n">
         <v>0</v>
       </c>
@@ -25230,10 +25240,10 @@
         <v>2</v>
       </c>
       <c r="CF43" s="46" t="n">
-        <v>0.3261</v>
+        <v>0.3761</v>
       </c>
       <c r="CG43" s="46" t="n">
-        <v>0.5704</v>
+        <v>0.5369</v>
       </c>
       <c r="CH43" s="29" t="n">
         <v>2</v>
@@ -25248,7 +25258,7 @@
         <v>2</v>
       </c>
       <c r="CL43" s="31" t="n">
-        <v>9507800</v>
+        <v>11791700</v>
       </c>
       <c r="CM43" s="32" t="n">
         <v>6</v>
@@ -25256,7 +25266,11 @@
       <c r="CN43" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="CO43" s="45" t="n"/>
+      <c r="CO43" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="CP43" s="29" t="n">
         <v>0</v>
       </c>
@@ -25270,7 +25284,7 @@
         <v>0.3636</v>
       </c>
       <c r="CT43" s="46" t="n">
-        <v>0.5072</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="CU43" s="29" t="n">
         <v>2</v>
@@ -25285,7 +25299,7 @@
         <v>2</v>
       </c>
       <c r="CY43" s="31" t="n">
-        <v>10575000</v>
+        <v>11844000</v>
       </c>
       <c r="CZ43" s="32" t="n">
         <v>6</v>
@@ -25311,7 +25325,7 @@
         <v>0.3435</v>
       </c>
       <c r="DG43" s="46" t="n">
-        <v>0.5078</v>
+        <v>0.4437</v>
       </c>
       <c r="DH43" s="29" t="n">
         <v>2</v>
@@ -25347,10 +25361,10 @@
         <v>2</v>
       </c>
       <c r="DS43" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT43" s="46" t="n">
-        <v>0.3939</v>
+        <v>0.5742</v>
       </c>
       <c r="DU43" s="29" t="n">
         <v>2</v>
@@ -25395,12 +25409,12 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>262826</t>
+          <t>66057</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>Mai Ngọc Lợi</t>
+          <t>Nguyễn Hồng Lợi</t>
         </is>
       </c>
       <c r="G44" s="39" t="inlineStr">
@@ -25423,7 +25437,7 @@
         <v>18</v>
       </c>
       <c r="L44" s="40" t="n">
-        <v>97184777</v>
+        <v>63237031</v>
       </c>
       <c r="M44" s="41" t="n">
         <v>52</v>
@@ -25446,13 +25460,13 @@
         <v>2</v>
       </c>
       <c r="S44" s="43" t="n">
-        <v>0.2387</v>
+        <v>0.2494</v>
       </c>
       <c r="T44" s="43" t="n">
-        <v>0.2203</v>
+        <v>0.3409</v>
       </c>
       <c r="U44" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" s="21" t="n">
         <v>0</v>
@@ -25464,15 +25478,19 @@
         <v>2</v>
       </c>
       <c r="Y44" s="23" t="n">
-        <v>11591000</v>
+        <v>5193000</v>
       </c>
       <c r="Z44" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB44" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AB44" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="AC44" s="21" t="n">
         <v>0</v>
       </c>
@@ -25483,10 +25501,10 @@
         <v>2</v>
       </c>
       <c r="AF44" s="43" t="n">
-        <v>0.2272</v>
+        <v>0.2092</v>
       </c>
       <c r="AG44" s="43" t="n">
-        <v>0.3832</v>
+        <v>0.5897</v>
       </c>
       <c r="AH44" s="21" t="n">
         <v>2</v>
@@ -25501,7 +25519,7 @@
         <v>2</v>
       </c>
       <c r="AL44" s="23" t="n">
-        <v>11174000</v>
+        <v>8787000</v>
       </c>
       <c r="AM44" s="24" t="n">
         <v>6</v>
@@ -25524,54 +25542,52 @@
         <v>2</v>
       </c>
       <c r="AS44" s="43" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AT44" s="43" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="AU44" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY44" s="23" t="n">
+        <v>11694000</v>
+      </c>
+      <c r="AZ44" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA44" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB44" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
+      <c r="BC44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF44" s="43" t="n">
         <v>0.4095</v>
       </c>
-      <c r="AT44" s="43" t="n">
-        <v>0.5764</v>
-      </c>
-      <c r="AU44" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV44" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY44" s="23" t="n">
-        <v>14891000</v>
-      </c>
-      <c r="AZ44" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA44" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB44" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
-      <c r="BC44" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE44" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF44" s="43" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="BG44" s="43" t="n">
-        <v>0.5371</v>
-      </c>
+      <c r="BG44" s="43" t="n"/>
       <c r="BH44" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI44" s="21" t="n">
         <v>0</v>
@@ -25583,19 +25599,15 @@
         <v>2</v>
       </c>
       <c r="BL44" s="23" t="n">
-        <v>15508846</v>
+        <v>7444000</v>
       </c>
       <c r="BM44" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BN44" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO44" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="BO44" s="39" t="n"/>
       <c r="BP44" s="21" t="n">
         <v>0</v>
       </c>
@@ -25606,10 +25618,10 @@
         <v>2</v>
       </c>
       <c r="BS44" s="43" t="n">
-        <v>0.431</v>
+        <v>0.3564</v>
       </c>
       <c r="BT44" s="43" t="n">
-        <v>0.4977</v>
+        <v>0.7179000000000001</v>
       </c>
       <c r="BU44" s="21" t="n">
         <v>2</v>
@@ -25624,7 +25636,7 @@
         <v>2</v>
       </c>
       <c r="BY44" s="23" t="n">
-        <v>20384231</v>
+        <v>10223231</v>
       </c>
       <c r="BZ44" s="24" t="n">
         <v>6</v>
@@ -25632,11 +25644,7 @@
       <c r="CA44" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="CB44" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+      <c r="CB44" s="39" t="n"/>
       <c r="CC44" s="21" t="n">
         <v>0</v>
       </c>
@@ -25647,10 +25655,10 @@
         <v>2</v>
       </c>
       <c r="CF44" s="43" t="n">
-        <v>0.3761</v>
+        <v>0.3261</v>
       </c>
       <c r="CG44" s="43" t="n">
-        <v>0.5369</v>
+        <v>0.4944</v>
       </c>
       <c r="CH44" s="21" t="n">
         <v>2</v>
@@ -25665,7 +25673,7 @@
         <v>2</v>
       </c>
       <c r="CL44" s="23" t="n">
-        <v>11791700</v>
+        <v>11379000</v>
       </c>
       <c r="CM44" s="24" t="n">
         <v>6</v>
@@ -25691,7 +25699,7 @@
         <v>0.3636</v>
       </c>
       <c r="CT44" s="43" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6636</v>
       </c>
       <c r="CU44" s="21" t="n">
         <v>2</v>
@@ -25706,7 +25714,7 @@
         <v>2</v>
       </c>
       <c r="CY44" s="23" t="n">
-        <v>11844000</v>
+        <v>8516800</v>
       </c>
       <c r="CZ44" s="24" t="n">
         <v>6</v>
@@ -25732,7 +25740,7 @@
         <v>0.3435</v>
       </c>
       <c r="DG44" s="43" t="n">
-        <v>0.4437</v>
+        <v>0.5192</v>
       </c>
       <c r="DH44" s="21" t="n">
         <v>2</v>
@@ -25768,10 +25776,10 @@
         <v>2</v>
       </c>
       <c r="DS44" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT44" s="43" t="n">
-        <v>0.5833</v>
+        <v>0.5</v>
       </c>
       <c r="DU44" s="21" t="n">
         <v>2</v>
@@ -25816,12 +25824,12 @@
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Lợi</t>
+          <t>Bùi Thanh Quang</t>
         </is>
       </c>
       <c r="G45" s="45" t="inlineStr">
@@ -25835,16 +25843,16 @@
         </is>
       </c>
       <c r="I45" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J45" s="17" t="n">
         <v>18</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>16</v>
       </c>
       <c r="K45" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L45" s="40" t="n">
-        <v>63237031</v>
+        <v>101787141</v>
       </c>
       <c r="M45" s="41" t="n">
         <v>52</v>
@@ -25867,10 +25875,10 @@
         <v>2</v>
       </c>
       <c r="S45" s="46" t="n">
-        <v>0.2494</v>
+        <v>0.2387</v>
       </c>
       <c r="T45" s="46" t="n">
-        <v>0.3409</v>
+        <v>0.4694</v>
       </c>
       <c r="U45" s="29" t="n">
         <v>2</v>
@@ -25885,7 +25893,7 @@
         <v>2</v>
       </c>
       <c r="Y45" s="31" t="n">
-        <v>5193000</v>
+        <v>15850333</v>
       </c>
       <c r="Z45" s="32" t="n">
         <v>6</v>
@@ -25908,10 +25916,10 @@
         <v>2</v>
       </c>
       <c r="AF45" s="46" t="n">
-        <v>0.2092</v>
+        <v>0.2272</v>
       </c>
       <c r="AG45" s="46" t="n">
-        <v>0.5897</v>
+        <v>0.3224</v>
       </c>
       <c r="AH45" s="29" t="n">
         <v>2</v>
@@ -25926,7 +25934,7 @@
         <v>2</v>
       </c>
       <c r="AL45" s="31" t="n">
-        <v>8787000</v>
+        <v>13276500</v>
       </c>
       <c r="AM45" s="32" t="n">
         <v>6</v>
@@ -25949,10 +25957,10 @@
         <v>2</v>
       </c>
       <c r="AS45" s="46" t="n">
-        <v>0.3277</v>
+        <v>0.4095</v>
       </c>
       <c r="AT45" s="46" t="n">
-        <v>0.6605</v>
+        <v>0.8951</v>
       </c>
       <c r="AU45" s="29" t="n">
         <v>2</v>
@@ -25967,7 +25975,7 @@
         <v>2</v>
       </c>
       <c r="AY45" s="31" t="n">
-        <v>11694000</v>
+        <v>15361923</v>
       </c>
       <c r="AZ45" s="32" t="n">
         <v>6</v>
@@ -25990,11 +25998,13 @@
         <v>2</v>
       </c>
       <c r="BF45" s="46" t="n">
-        <v>0.4095</v>
-      </c>
-      <c r="BG45" s="46" t="n"/>
+        <v>0.412</v>
+      </c>
+      <c r="BG45" s="46" t="n">
+        <v>0.8545</v>
+      </c>
       <c r="BH45" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI45" s="29" t="n">
         <v>0</v>
@@ -26006,15 +26016,19 @@
         <v>2</v>
       </c>
       <c r="BL45" s="31" t="n">
-        <v>7444000</v>
+        <v>11651154</v>
       </c>
       <c r="BM45" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN45" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO45" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="BO45" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="BP45" s="29" t="n">
         <v>0</v>
       </c>
@@ -26025,10 +26039,10 @@
         <v>2</v>
       </c>
       <c r="BS45" s="46" t="n">
-        <v>0.3564</v>
+        <v>0.431</v>
       </c>
       <c r="BT45" s="46" t="n">
-        <v>0.7179000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="BU45" s="29" t="n">
         <v>2</v>
@@ -26043,7 +26057,7 @@
         <v>2</v>
       </c>
       <c r="BY45" s="31" t="n">
-        <v>10223231</v>
+        <v>20314231</v>
       </c>
       <c r="BZ45" s="32" t="n">
         <v>6</v>
@@ -26051,7 +26065,11 @@
       <c r="CA45" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="CB45" s="45" t="n"/>
+      <c r="CB45" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="CC45" s="29" t="n">
         <v>0</v>
       </c>
@@ -26062,10 +26080,10 @@
         <v>2</v>
       </c>
       <c r="CF45" s="46" t="n">
-        <v>0.3261</v>
+        <v>0.3761</v>
       </c>
       <c r="CG45" s="46" t="n">
-        <v>0.4944</v>
+        <v>0.8616</v>
       </c>
       <c r="CH45" s="29" t="n">
         <v>2</v>
@@ -26080,7 +26098,7 @@
         <v>2</v>
       </c>
       <c r="CL45" s="31" t="n">
-        <v>11379000</v>
+        <v>12807000</v>
       </c>
       <c r="CM45" s="32" t="n">
         <v>6</v>
@@ -26106,7 +26124,7 @@
         <v>0.3636</v>
       </c>
       <c r="CT45" s="46" t="n">
-        <v>0.6636</v>
+        <v>0.8879</v>
       </c>
       <c r="CU45" s="29" t="n">
         <v>2</v>
@@ -26121,7 +26139,7 @@
         <v>2</v>
       </c>
       <c r="CY45" s="31" t="n">
-        <v>8516800</v>
+        <v>12526000</v>
       </c>
       <c r="CZ45" s="32" t="n">
         <v>6</v>
@@ -26138,16 +26156,16 @@
         <v>0</v>
       </c>
       <c r="DD45" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE45" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DF45" s="46" t="n">
         <v>0.3435</v>
       </c>
       <c r="DG45" s="46" t="n">
-        <v>0.5192</v>
+        <v>0.6443</v>
       </c>
       <c r="DH45" s="29" t="n">
         <v>2</v>
@@ -26163,16 +26181,12 @@
       </c>
       <c r="DL45" s="31" t="n"/>
       <c r="DM45" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="DN45" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO45" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="DO45" s="45" t="n"/>
       <c r="DP45" s="29" t="n">
         <v>0</v>
       </c>
@@ -26183,10 +26197,10 @@
         <v>2</v>
       </c>
       <c r="DS45" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT45" s="46" t="n">
-        <v>0.52</v>
+        <v>0.7327</v>
       </c>
       <c r="DU45" s="29" t="n">
         <v>2</v>
@@ -26231,12 +26245,12 @@
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>75187</t>
+          <t>171007</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>Bùi Thanh Quang</t>
+          <t>Nguyễn Trọng Tấn</t>
         </is>
       </c>
       <c r="G46" s="39" t="inlineStr">
@@ -26250,22 +26264,22 @@
         </is>
       </c>
       <c r="I46" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K46" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L46" s="40" t="n">
-        <v>101787141</v>
+        <v>77482493</v>
       </c>
       <c r="M46" s="41" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N46" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O46" s="42" t="inlineStr">
         <is>
@@ -26282,13 +26296,13 @@
         <v>2</v>
       </c>
       <c r="S46" s="43" t="n">
-        <v>0.2387</v>
+        <v>0.2494</v>
       </c>
       <c r="T46" s="43" t="n">
-        <v>0.4694</v>
+        <v>0.0207</v>
       </c>
       <c r="U46" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V46" s="21" t="n">
         <v>0</v>
@@ -26300,60 +26314,56 @@
         <v>2</v>
       </c>
       <c r="Y46" s="23" t="n">
-        <v>15850333</v>
+        <v>9797000</v>
       </c>
       <c r="Z46" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="44" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="AB46" s="39" t="n"/>
+      <c r="AC46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" s="43" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="AG46" s="43" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AH46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL46" s="23" t="n">
+        <v>13171000</v>
+      </c>
+      <c r="AM46" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="44" t="inlineStr">
         <is>
           <t>VƯỢT TRỘI</t>
         </is>
       </c>
-      <c r="AC46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF46" s="43" t="n">
-        <v>0.2272</v>
-      </c>
-      <c r="AG46" s="43" t="n">
-        <v>0.3224</v>
-      </c>
-      <c r="AH46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL46" s="23" t="n">
-        <v>13276500</v>
-      </c>
-      <c r="AM46" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
       <c r="AP46" s="21" t="n">
         <v>0</v>
       </c>
@@ -26364,51 +26374,47 @@
         <v>2</v>
       </c>
       <c r="AS46" s="43" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AT46" s="43" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="AU46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY46" s="23" t="n">
+        <v>10920000</v>
+      </c>
+      <c r="AZ46" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA46" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB46" s="39" t="n"/>
+      <c r="BC46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF46" s="43" t="n">
         <v>0.4095</v>
       </c>
-      <c r="AT46" s="43" t="n">
-        <v>0.8951</v>
-      </c>
-      <c r="AU46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY46" s="23" t="n">
-        <v>15361923</v>
-      </c>
-      <c r="AZ46" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
-      <c r="BC46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF46" s="43" t="n">
-        <v>0.412</v>
-      </c>
       <c r="BG46" s="43" t="n">
-        <v>0.8545</v>
+        <v>0.5962</v>
       </c>
       <c r="BH46" s="21" t="n">
         <v>2</v>
@@ -26423,7 +26429,7 @@
         <v>2</v>
       </c>
       <c r="BL46" s="23" t="n">
-        <v>11651154</v>
+        <v>9087462</v>
       </c>
       <c r="BM46" s="24" t="n">
         <v>6</v>
@@ -26431,11 +26437,7 @@
       <c r="BN46" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="BO46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+      <c r="BO46" s="39" t="n"/>
       <c r="BP46" s="21" t="n">
         <v>0</v>
       </c>
@@ -26446,10 +26448,10 @@
         <v>2</v>
       </c>
       <c r="BS46" s="43" t="n">
-        <v>0.431</v>
+        <v>0.3564</v>
       </c>
       <c r="BT46" s="43" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.5211</v>
       </c>
       <c r="BU46" s="21" t="n">
         <v>2</v>
@@ -26464,7 +26466,7 @@
         <v>2</v>
       </c>
       <c r="BY46" s="23" t="n">
-        <v>20314231</v>
+        <v>14424231</v>
       </c>
       <c r="BZ46" s="24" t="n">
         <v>6</v>
@@ -26472,11 +26474,7 @@
       <c r="CA46" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="CB46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+      <c r="CB46" s="39" t="n"/>
       <c r="CC46" s="21" t="n">
         <v>0</v>
       </c>
@@ -26487,10 +26485,10 @@
         <v>2</v>
       </c>
       <c r="CF46" s="43" t="n">
-        <v>0.3761</v>
+        <v>0.3261</v>
       </c>
       <c r="CG46" s="43" t="n">
-        <v>0.8616</v>
+        <v>0.5704</v>
       </c>
       <c r="CH46" s="21" t="n">
         <v>2</v>
@@ -26505,7 +26503,7 @@
         <v>2</v>
       </c>
       <c r="CL46" s="23" t="n">
-        <v>12807000</v>
+        <v>9507800</v>
       </c>
       <c r="CM46" s="24" t="n">
         <v>6</v>
@@ -26513,11 +26511,7 @@
       <c r="CN46" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="CO46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+      <c r="CO46" s="39" t="n"/>
       <c r="CP46" s="21" t="n">
         <v>0</v>
       </c>
@@ -26531,7 +26525,7 @@
         <v>0.3636</v>
       </c>
       <c r="CT46" s="43" t="n">
-        <v>0.8879</v>
+        <v>0.5072</v>
       </c>
       <c r="CU46" s="21" t="n">
         <v>2</v>
@@ -26546,7 +26540,7 @@
         <v>2</v>
       </c>
       <c r="CY46" s="23" t="n">
-        <v>12526000</v>
+        <v>10575000</v>
       </c>
       <c r="CZ46" s="24" t="n">
         <v>6</v>
@@ -26563,16 +26557,16 @@
         <v>0</v>
       </c>
       <c r="DD46" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE46" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DF46" s="43" t="n">
         <v>0.3435</v>
       </c>
       <c r="DG46" s="43" t="n">
-        <v>0.6443</v>
+        <v>0.5078</v>
       </c>
       <c r="DH46" s="21" t="n">
         <v>2</v>
@@ -26588,12 +26582,16 @@
       </c>
       <c r="DL46" s="23" t="n"/>
       <c r="DM46" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DN46" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="DO46" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="DO46" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="DP46" s="21" t="n">
         <v>0</v>
       </c>
@@ -26604,13 +26602,13 @@
         <v>2</v>
       </c>
       <c r="DS46" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT46" s="43" t="n">
-        <v>0.6716</v>
+        <v>0.3211</v>
       </c>
       <c r="DU46" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV46" s="21" t="n">
         <v>0</v>
@@ -26623,16 +26621,12 @@
       </c>
       <c r="DY46" s="23" t="n"/>
       <c r="DZ46" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB46" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="EB46" s="39" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
@@ -26674,7 +26668,7 @@
         <v>18</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K47" s="17" t="n">
         <v>18</v>
@@ -26683,12 +26677,16 @@
         <v>88185778</v>
       </c>
       <c r="M47" s="41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N47" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="O47" s="47" t="n"/>
+      <c r="O47" s="42" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="P47" s="29" t="n">
         <v>0</v>
       </c>
@@ -27013,13 +27011,13 @@
         <v>2</v>
       </c>
       <c r="DS47" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT47" s="46" t="n">
-        <v>0.3714</v>
+        <v>0.4466</v>
       </c>
       <c r="DU47" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV47" s="29" t="n">
         <v>0</v>
@@ -27032,12 +27030,16 @@
       </c>
       <c r="DY47" s="31" t="n"/>
       <c r="DZ47" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EA47" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="EB47" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="EB47" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="14" t="inlineStr">
@@ -27091,13 +27093,9 @@
         <v>46</v>
       </c>
       <c r="N48" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O48" s="42" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O48" s="47" t="n"/>
       <c r="P48" s="21" t="n">
         <v>0</v>
       </c>
@@ -27422,10 +27420,10 @@
         <v>2</v>
       </c>
       <c r="DS48" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT48" s="43" t="n">
-        <v>0.3051</v>
+        <v>0.3448</v>
       </c>
       <c r="DU48" s="21" t="n">
         <v>0</v>
@@ -27444,7 +27442,7 @@
         <v>4</v>
       </c>
       <c r="EA48" s="21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB48" s="39" t="n"/>
     </row>
@@ -27790,10 +27788,10 @@
         <v>2</v>
       </c>
       <c r="DS49" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT49" s="46" t="n">
-        <v>0.4043</v>
+        <v>0.5032</v>
       </c>
       <c r="DU49" s="29" t="n">
         <v>2</v>
@@ -28177,10 +28175,10 @@
         <v>2</v>
       </c>
       <c r="DS50" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT50" s="43" t="n">
-        <v>0.7</v>
+        <v>0.7064</v>
       </c>
       <c r="DU50" s="21" t="n">
         <v>2</v>
@@ -28582,10 +28580,10 @@
         <v>2</v>
       </c>
       <c r="DS51" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT51" s="46" t="n">
-        <v>0.1061</v>
+        <v>0.1458</v>
       </c>
       <c r="DU51" s="29" t="n">
         <v>0</v>
@@ -28604,7 +28602,7 @@
         <v>4</v>
       </c>
       <c r="EA51" s="29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB51" s="45" t="n"/>
     </row>
@@ -28971,10 +28969,10 @@
         <v>2</v>
       </c>
       <c r="DS52" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT52" s="43" t="n">
-        <v>0.4301</v>
+        <v>0.4465</v>
       </c>
       <c r="DU52" s="21" t="n">
         <v>2</v>
@@ -29364,10 +29362,10 @@
         <v>2</v>
       </c>
       <c r="DS53" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT53" s="46" t="n">
-        <v>0.2371</v>
+        <v>0.2877</v>
       </c>
       <c r="DU53" s="29" t="n">
         <v>0</v>
@@ -29386,7 +29384,7 @@
         <v>4</v>
       </c>
       <c r="EA53" s="29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB53" s="45" t="n"/>
     </row>
@@ -29753,10 +29751,10 @@
         <v>2</v>
       </c>
       <c r="DS54" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT54" s="43" t="n">
-        <v>0.1837</v>
+        <v>0.284</v>
       </c>
       <c r="DU54" s="21" t="n">
         <v>0</v>
@@ -29775,7 +29773,7 @@
         <v>4</v>
       </c>
       <c r="EA54" s="21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB54" s="39" t="n"/>
     </row>
@@ -29797,12 +29795,12 @@
       </c>
       <c r="E55" s="26" t="inlineStr">
         <is>
-          <t>49813</t>
+          <t>53172</t>
         </is>
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>Lê Thành Phong</t>
+          <t>Lê Tân Phong</t>
         </is>
       </c>
       <c r="G55" s="45" t="inlineStr">
@@ -29816,16 +29814,16 @@
         </is>
       </c>
       <c r="I55" s="17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K55" s="17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>32958131</v>
+        <v>81083652</v>
       </c>
       <c r="M55" s="41" t="n">
         <v>36</v>
@@ -29841,12 +29839,14 @@
         <v>0</v>
       </c>
       <c r="R55" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55" s="46" t="n">
         <v>0.2494</v>
       </c>
-      <c r="T55" s="46" t="n"/>
+      <c r="T55" s="46" t="n">
+        <v>0.0876</v>
+      </c>
       <c r="U55" s="29" t="n">
         <v>0</v>
       </c>
@@ -29857,14 +29857,16 @@
         <v>0</v>
       </c>
       <c r="X55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="31" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="Y55" s="31" t="n">
+        <v>11790185</v>
+      </c>
       <c r="Z55" s="32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA55" s="29" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AB55" s="45" t="n"/>
       <c r="AC55" s="29" t="n">
@@ -29874,12 +29876,14 @@
         <v>0</v>
       </c>
       <c r="AE55" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF55" s="46" t="n">
         <v>0.2092</v>
       </c>
-      <c r="AG55" s="46" t="n"/>
+      <c r="AG55" s="46" t="n">
+        <v>0.0462</v>
+      </c>
       <c r="AH55" s="29" t="n">
         <v>0</v>
       </c>
@@ -29890,14 +29894,16 @@
         <v>0</v>
       </c>
       <c r="AK55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" s="31" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="AL55" s="31" t="n">
+        <v>14084417</v>
+      </c>
       <c r="AM55" s="32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN55" s="29" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AO55" s="45" t="n"/>
       <c r="AP55" s="29" t="n">
@@ -29913,7 +29919,7 @@
         <v>0.3277</v>
       </c>
       <c r="AT55" s="46" t="n">
-        <v>0.1852</v>
+        <v>0.1947</v>
       </c>
       <c r="AU55" s="29" t="n">
         <v>0</v>
@@ -29928,7 +29934,7 @@
         <v>2</v>
       </c>
       <c r="AY55" s="31" t="n">
-        <v>2051000</v>
+        <v>12364923</v>
       </c>
       <c r="AZ55" s="32" t="n">
         <v>4</v>
@@ -29949,9 +29955,7 @@
       <c r="BF55" s="46" t="n">
         <v>0.4095</v>
       </c>
-      <c r="BG55" s="46" t="n">
-        <v>0.2656</v>
-      </c>
+      <c r="BG55" s="46" t="n"/>
       <c r="BH55" s="29" t="n">
         <v>0</v>
       </c>
@@ -29959,19 +29963,19 @@
         <v>0</v>
       </c>
       <c r="BJ55" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK55" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL55" s="31" t="n">
-        <v>4563100</v>
+        <v>10793846</v>
       </c>
       <c r="BM55" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN55" s="29" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BO55" s="45" t="n"/>
       <c r="BP55" s="29" t="n">
@@ -29987,10 +29991,10 @@
         <v>0.3564</v>
       </c>
       <c r="BT55" s="46" t="n">
-        <v>0.44</v>
+        <v>0.1079</v>
       </c>
       <c r="BU55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BV55" s="29" t="n">
         <v>0</v>
@@ -30002,13 +30006,13 @@
         <v>2</v>
       </c>
       <c r="BY55" s="31" t="n">
-        <v>9890231</v>
+        <v>14998231</v>
       </c>
       <c r="BZ55" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CA55" s="29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="CB55" s="45" t="n"/>
       <c r="CC55" s="29" t="n">
@@ -30024,10 +30028,10 @@
         <v>0.3261</v>
       </c>
       <c r="CG55" s="46" t="n">
-        <v>0.6738</v>
+        <v>0.2468</v>
       </c>
       <c r="CH55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CI55" s="29" t="n">
         <v>0</v>
@@ -30039,13 +30043,13 @@
         <v>2</v>
       </c>
       <c r="CL55" s="31" t="n">
-        <v>9761000</v>
+        <v>9364000</v>
       </c>
       <c r="CM55" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN55" s="29" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="CO55" s="45" t="n"/>
       <c r="CP55" s="29" t="n">
@@ -30061,10 +30065,10 @@
         <v>0.3636</v>
       </c>
       <c r="CT55" s="46" t="n">
-        <v>0.6824</v>
+        <v>0.2364</v>
       </c>
       <c r="CU55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV55" s="29" t="n">
         <v>0</v>
@@ -30076,13 +30080,13 @@
         <v>2</v>
       </c>
       <c r="CY55" s="31" t="n">
-        <v>6692800</v>
+        <v>7688050</v>
       </c>
       <c r="CZ55" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="DA55" s="29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="DB55" s="45" t="n"/>
       <c r="DC55" s="29" t="n">
@@ -30098,10 +30102,10 @@
         <v>0.3435</v>
       </c>
       <c r="DG55" s="46" t="n">
-        <v>0.7087</v>
+        <v>0.1463</v>
       </c>
       <c r="DH55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DI55" s="29" t="n">
         <v>0</v>
@@ -30114,16 +30118,12 @@
       </c>
       <c r="DL55" s="31" t="n"/>
       <c r="DM55" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="DN55" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO55" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="DO55" s="45" t="n"/>
       <c r="DP55" s="29" t="n">
         <v>0</v>
       </c>
@@ -30134,13 +30134,13 @@
         <v>2</v>
       </c>
       <c r="DS55" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT55" s="46" t="n">
-        <v>0.6842</v>
+        <v>0.3374</v>
       </c>
       <c r="DU55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV55" s="29" t="n">
         <v>0</v>
@@ -30153,16 +30153,12 @@
       </c>
       <c r="DY55" s="31" t="n"/>
       <c r="DZ55" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA55" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB55" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="EB55" s="45" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="14" t="inlineStr">
@@ -30182,12 +30178,12 @@
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>53172</t>
+          <t>254006</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>Lê Tân Phong</t>
+          <t>Đặng Thanh Toàn</t>
         </is>
       </c>
       <c r="G56" s="39" t="inlineStr">
@@ -30201,22 +30197,22 @@
         </is>
       </c>
       <c r="I56" s="17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L56" s="40" t="n">
-        <v>81083652</v>
+        <v>100160793</v>
       </c>
       <c r="M56" s="41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N56" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O56" s="47" t="n"/>
       <c r="P56" s="21" t="n">
@@ -30232,10 +30228,10 @@
         <v>0.2494</v>
       </c>
       <c r="T56" s="43" t="n">
-        <v>0.0876</v>
+        <v>0.2789</v>
       </c>
       <c r="U56" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V56" s="21" t="n">
         <v>0</v>
@@ -30247,15 +30243,19 @@
         <v>2</v>
       </c>
       <c r="Y56" s="23" t="n">
-        <v>11790185</v>
+        <v>16505000</v>
       </c>
       <c r="Z56" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA56" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB56" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AB56" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="AC56" s="21" t="n">
         <v>0</v>
       </c>
@@ -30269,7 +30269,7 @@
         <v>0.2092</v>
       </c>
       <c r="AG56" s="43" t="n">
-        <v>0.0462</v>
+        <v>0.1</v>
       </c>
       <c r="AH56" s="21" t="n">
         <v>0</v>
@@ -30284,7 +30284,7 @@
         <v>2</v>
       </c>
       <c r="AL56" s="23" t="n">
-        <v>14084417</v>
+        <v>13503300</v>
       </c>
       <c r="AM56" s="24" t="n">
         <v>4</v>
@@ -30306,7 +30306,7 @@
         <v>0.3277</v>
       </c>
       <c r="AT56" s="43" t="n">
-        <v>0.1947</v>
+        <v>0.3243</v>
       </c>
       <c r="AU56" s="21" t="n">
         <v>0</v>
@@ -30321,7 +30321,7 @@
         <v>2</v>
       </c>
       <c r="AY56" s="23" t="n">
-        <v>12364923</v>
+        <v>16054000</v>
       </c>
       <c r="AZ56" s="24" t="n">
         <v>4</v>
@@ -30342,7 +30342,9 @@
       <c r="BF56" s="43" t="n">
         <v>0.4095</v>
       </c>
-      <c r="BG56" s="43" t="n"/>
+      <c r="BG56" s="43" t="n">
+        <v>0.3605</v>
+      </c>
       <c r="BH56" s="21" t="n">
         <v>0</v>
       </c>
@@ -30356,7 +30358,7 @@
         <v>2</v>
       </c>
       <c r="BL56" s="23" t="n">
-        <v>10793846</v>
+        <v>12577462</v>
       </c>
       <c r="BM56" s="24" t="n">
         <v>4</v>
@@ -30378,7 +30380,7 @@
         <v>0.3564</v>
       </c>
       <c r="BT56" s="43" t="n">
-        <v>0.1079</v>
+        <v>0.3034</v>
       </c>
       <c r="BU56" s="21" t="n">
         <v>0</v>
@@ -30393,7 +30395,7 @@
         <v>2</v>
       </c>
       <c r="BY56" s="23" t="n">
-        <v>14998231</v>
+        <v>15879231</v>
       </c>
       <c r="BZ56" s="24" t="n">
         <v>4</v>
@@ -30415,7 +30417,7 @@
         <v>0.3261</v>
       </c>
       <c r="CG56" s="43" t="n">
-        <v>0.2468</v>
+        <v>0.1069</v>
       </c>
       <c r="CH56" s="21" t="n">
         <v>0</v>
@@ -30430,7 +30432,7 @@
         <v>2</v>
       </c>
       <c r="CL56" s="23" t="n">
-        <v>9364000</v>
+        <v>12941800</v>
       </c>
       <c r="CM56" s="24" t="n">
         <v>4</v>
@@ -30443,16 +30445,16 @@
         <v>0</v>
       </c>
       <c r="CQ56" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR56" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CS56" s="43" t="n">
         <v>0.3636</v>
       </c>
       <c r="CT56" s="43" t="n">
-        <v>0.2364</v>
+        <v>0.1133</v>
       </c>
       <c r="CU56" s="21" t="n">
         <v>0</v>
@@ -30467,29 +30469,29 @@
         <v>2</v>
       </c>
       <c r="CY56" s="23" t="n">
-        <v>7688050</v>
+        <v>12700000</v>
       </c>
       <c r="CZ56" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DA56" s="21" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="DB56" s="39" t="n"/>
       <c r="DC56" s="21" t="n">
         <v>0</v>
       </c>
       <c r="DD56" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE56" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DF56" s="43" t="n">
         <v>0.3435</v>
       </c>
       <c r="DG56" s="43" t="n">
-        <v>0.1463</v>
+        <v>0.1795</v>
       </c>
       <c r="DH56" s="21" t="n">
         <v>0</v>
@@ -30505,10 +30507,10 @@
       </c>
       <c r="DL56" s="23" t="n"/>
       <c r="DM56" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DN56" s="21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="DO56" s="39" t="n"/>
       <c r="DP56" s="21" t="n">
@@ -30521,10 +30523,10 @@
         <v>2</v>
       </c>
       <c r="DS56" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT56" s="43" t="n">
-        <v>0.2212</v>
+        <v>0.2704</v>
       </c>
       <c r="DU56" s="21" t="n">
         <v>0</v>
@@ -30543,7 +30545,7 @@
         <v>4</v>
       </c>
       <c r="EA56" s="21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB56" s="39" t="n"/>
     </row>
@@ -30565,12 +30567,12 @@
       </c>
       <c r="E57" s="26" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>Đặng Thanh Toàn</t>
+          <t>Lê Thành Phong</t>
         </is>
       </c>
       <c r="G57" s="45" t="inlineStr">
@@ -30584,22 +30586,22 @@
         </is>
       </c>
       <c r="I57" s="17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K57" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L57" s="40" t="n">
-        <v>100160793</v>
+        <v>32958131</v>
       </c>
       <c r="M57" s="41" t="n">
         <v>34</v>
       </c>
       <c r="N57" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O57" s="47" t="n"/>
       <c r="P57" s="29" t="n">
@@ -30609,16 +30611,14 @@
         <v>0</v>
       </c>
       <c r="R57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S57" s="46" t="n">
         <v>0.2494</v>
       </c>
-      <c r="T57" s="46" t="n">
-        <v>0.2789</v>
-      </c>
+      <c r="T57" s="46" t="n"/>
       <c r="U57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V57" s="29" t="n">
         <v>0</v>
@@ -30627,22 +30627,16 @@
         <v>0</v>
       </c>
       <c r="X57" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y57" s="31" t="n">
-        <v>16505000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="31" t="n"/>
       <c r="Z57" s="32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB57" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="AB57" s="45" t="n"/>
       <c r="AC57" s="29" t="n">
         <v>0</v>
       </c>
@@ -30650,14 +30644,12 @@
         <v>0</v>
       </c>
       <c r="AE57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="46" t="n">
         <v>0.2092</v>
       </c>
-      <c r="AG57" s="46" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="AG57" s="46" t="n"/>
       <c r="AH57" s="29" t="n">
         <v>0</v>
       </c>
@@ -30668,16 +30660,14 @@
         <v>0</v>
       </c>
       <c r="AK57" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL57" s="31" t="n">
-        <v>13503300</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL57" s="31" t="n"/>
       <c r="AM57" s="32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN57" s="29" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AO57" s="45" t="n"/>
       <c r="AP57" s="29" t="n">
@@ -30693,7 +30683,7 @@
         <v>0.3277</v>
       </c>
       <c r="AT57" s="46" t="n">
-        <v>0.3243</v>
+        <v>0.1852</v>
       </c>
       <c r="AU57" s="29" t="n">
         <v>0</v>
@@ -30708,7 +30698,7 @@
         <v>2</v>
       </c>
       <c r="AY57" s="31" t="n">
-        <v>16054000</v>
+        <v>2051000</v>
       </c>
       <c r="AZ57" s="32" t="n">
         <v>4</v>
@@ -30730,7 +30720,7 @@
         <v>0.4095</v>
       </c>
       <c r="BG57" s="46" t="n">
-        <v>0.3605</v>
+        <v>0.2656</v>
       </c>
       <c r="BH57" s="29" t="n">
         <v>0</v>
@@ -30739,19 +30729,19 @@
         <v>0</v>
       </c>
       <c r="BJ57" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL57" s="31" t="n">
-        <v>12577462</v>
+        <v>4563100</v>
       </c>
       <c r="BM57" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN57" s="29" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BO57" s="45" t="n"/>
       <c r="BP57" s="29" t="n">
@@ -30767,10 +30757,10 @@
         <v>0.3564</v>
       </c>
       <c r="BT57" s="46" t="n">
-        <v>0.3034</v>
+        <v>0.44</v>
       </c>
       <c r="BU57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BV57" s="29" t="n">
         <v>0</v>
@@ -30782,13 +30772,13 @@
         <v>2</v>
       </c>
       <c r="BY57" s="31" t="n">
-        <v>15879231</v>
+        <v>9890231</v>
       </c>
       <c r="BZ57" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CA57" s="29" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="CB57" s="45" t="n"/>
       <c r="CC57" s="29" t="n">
@@ -30804,10 +30794,10 @@
         <v>0.3261</v>
       </c>
       <c r="CG57" s="46" t="n">
-        <v>0.1069</v>
+        <v>0.6738</v>
       </c>
       <c r="CH57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CI57" s="29" t="n">
         <v>0</v>
@@ -30819,32 +30809,32 @@
         <v>2</v>
       </c>
       <c r="CL57" s="31" t="n">
-        <v>12941800</v>
+        <v>9761000</v>
       </c>
       <c r="CM57" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN57" s="29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="CO57" s="45" t="n"/>
       <c r="CP57" s="29" t="n">
         <v>0</v>
       </c>
       <c r="CQ57" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CS57" s="46" t="n">
         <v>0.3636</v>
       </c>
       <c r="CT57" s="46" t="n">
-        <v>0.1133</v>
+        <v>0.6824</v>
       </c>
       <c r="CU57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV57" s="29" t="n">
         <v>0</v>
@@ -30856,32 +30846,32 @@
         <v>2</v>
       </c>
       <c r="CY57" s="31" t="n">
-        <v>12700000</v>
+        <v>6692800</v>
       </c>
       <c r="CZ57" s="32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="DA57" s="29" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="DB57" s="45" t="n"/>
       <c r="DC57" s="29" t="n">
         <v>0</v>
       </c>
       <c r="DD57" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DF57" s="46" t="n">
         <v>0.3435</v>
       </c>
       <c r="DG57" s="46" t="n">
-        <v>0.1795</v>
+        <v>0.7087</v>
       </c>
       <c r="DH57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DI57" s="29" t="n">
         <v>0</v>
@@ -30894,29 +30884,33 @@
       </c>
       <c r="DL57" s="31" t="n"/>
       <c r="DM57" s="32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="DN57" s="29" t="n">
-        <v>19</v>
-      </c>
-      <c r="DO57" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="DO57" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="DP57" s="29" t="n">
         <v>0</v>
       </c>
       <c r="DQ57" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS57" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT57" s="46" t="n">
-        <v>0.2137</v>
+        <v>0.635</v>
       </c>
       <c r="DU57" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV57" s="29" t="n">
         <v>0</v>
@@ -30932,7 +30926,7 @@
         <v>4</v>
       </c>
       <c r="EA57" s="29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB57" s="45" t="n"/>
     </row>
@@ -30988,7 +30982,7 @@
         <v>34</v>
       </c>
       <c r="N58" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O58" s="47" t="n"/>
       <c r="P58" s="21" t="n">
@@ -31293,10 +31287,10 @@
         <v>2</v>
       </c>
       <c r="DS58" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT58" s="43" t="n">
-        <v>0.125</v>
+        <v>0.3137</v>
       </c>
       <c r="DU58" s="21" t="n">
         <v>0</v>
@@ -31315,7 +31309,7 @@
         <v>4</v>
       </c>
       <c r="EA58" s="21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB58" s="39" t="n"/>
     </row>
@@ -31371,7 +31365,7 @@
         <v>34</v>
       </c>
       <c r="N59" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O59" s="47" t="n"/>
       <c r="P59" s="29" t="n">
@@ -31676,10 +31670,10 @@
         <v>2</v>
       </c>
       <c r="DS59" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT59" s="46" t="n">
-        <v>0.1695</v>
+        <v>0.2435</v>
       </c>
       <c r="DU59" s="29" t="n">
         <v>0</v>
@@ -31698,7 +31692,7 @@
         <v>4</v>
       </c>
       <c r="EA59" s="29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB59" s="45" t="n"/>
     </row>
@@ -31720,12 +31714,12 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>284580</t>
+          <t>275387</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>Nguyễn Duy Tín</t>
+          <t>Lê Quốc Trọng</t>
         </is>
       </c>
       <c r="G60" s="39" t="inlineStr">
@@ -31742,16 +31736,16 @@
         <v>10</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K60" s="17" t="n">
         <v>10</v>
       </c>
       <c r="L60" s="40" t="n">
-        <v>24119655</v>
+        <v>20682314</v>
       </c>
       <c r="M60" s="41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N60" s="17" t="n">
         <v>19</v>
@@ -31830,12 +31824,14 @@
         <v>0</v>
       </c>
       <c r="AR60" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS60" s="43" t="n">
         <v>0.3277</v>
       </c>
-      <c r="AT60" s="43" t="n"/>
+      <c r="AT60" s="43" t="n">
+        <v>0.0256</v>
+      </c>
       <c r="AU60" s="21" t="n">
         <v>0</v>
       </c>
@@ -31846,14 +31842,16 @@
         <v>0</v>
       </c>
       <c r="AX60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" s="23" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="AY60" s="23" t="n">
+        <v>4539000</v>
+      </c>
       <c r="AZ60" s="24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA60" s="21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BB60" s="39" t="n"/>
       <c r="BC60" s="21" t="n">
@@ -31863,12 +31861,14 @@
         <v>0</v>
       </c>
       <c r="BE60" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF60" s="43" t="n">
         <v>0.4095</v>
       </c>
-      <c r="BG60" s="43" t="n"/>
+      <c r="BG60" s="43" t="n">
+        <v>0.0964</v>
+      </c>
       <c r="BH60" s="21" t="n">
         <v>0</v>
       </c>
@@ -31879,14 +31879,16 @@
         <v>0</v>
       </c>
       <c r="BK60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL60" s="23" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="BL60" s="23" t="n">
+        <v>7307000</v>
+      </c>
       <c r="BM60" s="24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN60" s="21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BO60" s="39" t="n"/>
       <c r="BP60" s="21" t="n">
@@ -31901,7 +31903,9 @@
       <c r="BS60" s="43" t="n">
         <v>0.3564</v>
       </c>
-      <c r="BT60" s="43" t="n"/>
+      <c r="BT60" s="43" t="n">
+        <v>0.1098</v>
+      </c>
       <c r="BU60" s="21" t="n">
         <v>0</v>
       </c>
@@ -31915,7 +31919,7 @@
         <v>2</v>
       </c>
       <c r="BY60" s="23" t="n">
-        <v>3411655</v>
+        <v>6764231</v>
       </c>
       <c r="BZ60" s="24" t="n">
         <v>4</v>
@@ -31937,7 +31941,7 @@
         <v>0.3261</v>
       </c>
       <c r="CG60" s="43" t="n">
-        <v>0.1769</v>
+        <v>0.02</v>
       </c>
       <c r="CH60" s="21" t="n">
         <v>0</v>
@@ -31952,7 +31956,7 @@
         <v>2</v>
       </c>
       <c r="CL60" s="23" t="n">
-        <v>9812000</v>
+        <v>2072000</v>
       </c>
       <c r="CM60" s="24" t="n">
         <v>4</v>
@@ -31973,9 +31977,7 @@
       <c r="CS60" s="43" t="n">
         <v>0.3636</v>
       </c>
-      <c r="CT60" s="43" t="n">
-        <v>0.1069</v>
-      </c>
+      <c r="CT60" s="43" t="n"/>
       <c r="CU60" s="21" t="n">
         <v>0</v>
       </c>
@@ -31989,7 +31991,7 @@
         <v>2</v>
       </c>
       <c r="CY60" s="23" t="n">
-        <v>10896000</v>
+        <v>83</v>
       </c>
       <c r="CZ60" s="24" t="n">
         <v>4</v>
@@ -31998,80 +32000,6 @@
         <v>10</v>
       </c>
       <c r="DB60" s="39" t="n"/>
-      <c r="DC60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF60" s="43" t="n">
-        <v>0.3435</v>
-      </c>
-      <c r="DG60" s="43" t="n">
-        <v>0.2587</v>
-      </c>
-      <c r="DH60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="DL60" s="23" t="n"/>
-      <c r="DM60" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="DN60" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="DO60" s="39" t="n"/>
-      <c r="DP60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="DS60" s="43" t="n">
-        <v>0.3739</v>
-      </c>
-      <c r="DT60" s="43" t="n">
-        <v>0.5647</v>
-      </c>
-      <c r="DU60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="DV60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX60" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="DY60" s="23" t="n"/>
-      <c r="DZ60" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="EA60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB60" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
@@ -32091,12 +32019,12 @@
       </c>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>275387</t>
+          <t>284580</t>
         </is>
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>Lê Quốc Trọng</t>
+          <t>Nguyễn Duy Tín</t>
         </is>
       </c>
       <c r="G61" s="45" t="inlineStr">
@@ -32110,22 +32038,22 @@
         </is>
       </c>
       <c r="I61" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="17" t="n">
         <v>10</v>
       </c>
       <c r="L61" s="40" t="n">
-        <v>20682314</v>
+        <v>24119655</v>
       </c>
       <c r="M61" s="41" t="n">
         <v>20</v>
       </c>
       <c r="N61" s="17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O61" s="47" t="n"/>
       <c r="P61" s="29" t="n">
@@ -32201,14 +32129,12 @@
         <v>0</v>
       </c>
       <c r="AR61" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS61" s="46" t="n">
         <v>0.3277</v>
       </c>
-      <c r="AT61" s="46" t="n">
-        <v>0.0256</v>
-      </c>
+      <c r="AT61" s="46" t="n"/>
       <c r="AU61" s="29" t="n">
         <v>0</v>
       </c>
@@ -32219,16 +32145,14 @@
         <v>0</v>
       </c>
       <c r="AX61" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY61" s="31" t="n">
-        <v>4539000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY61" s="31" t="n"/>
       <c r="AZ61" s="32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA61" s="29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BB61" s="45" t="n"/>
       <c r="BC61" s="29" t="n">
@@ -32238,14 +32162,12 @@
         <v>0</v>
       </c>
       <c r="BE61" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF61" s="46" t="n">
         <v>0.4095</v>
       </c>
-      <c r="BG61" s="46" t="n">
-        <v>0.0964</v>
-      </c>
+      <c r="BG61" s="46" t="n"/>
       <c r="BH61" s="29" t="n">
         <v>0</v>
       </c>
@@ -32256,16 +32178,14 @@
         <v>0</v>
       </c>
       <c r="BK61" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL61" s="31" t="n">
-        <v>7307000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BL61" s="31" t="n"/>
       <c r="BM61" s="32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BN61" s="29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BO61" s="45" t="n"/>
       <c r="BP61" s="29" t="n">
@@ -32280,9 +32200,7 @@
       <c r="BS61" s="46" t="n">
         <v>0.3564</v>
       </c>
-      <c r="BT61" s="46" t="n">
-        <v>0.1098</v>
-      </c>
+      <c r="BT61" s="46" t="n"/>
       <c r="BU61" s="29" t="n">
         <v>0</v>
       </c>
@@ -32296,7 +32214,7 @@
         <v>2</v>
       </c>
       <c r="BY61" s="31" t="n">
-        <v>6764231</v>
+        <v>3411655</v>
       </c>
       <c r="BZ61" s="32" t="n">
         <v>4</v>
@@ -32318,7 +32236,7 @@
         <v>0.3261</v>
       </c>
       <c r="CG61" s="46" t="n">
-        <v>0.02</v>
+        <v>0.1769</v>
       </c>
       <c r="CH61" s="29" t="n">
         <v>0</v>
@@ -32333,7 +32251,7 @@
         <v>2</v>
       </c>
       <c r="CL61" s="31" t="n">
-        <v>2072000</v>
+        <v>9812000</v>
       </c>
       <c r="CM61" s="32" t="n">
         <v>4</v>
@@ -32354,7 +32272,9 @@
       <c r="CS61" s="46" t="n">
         <v>0.3636</v>
       </c>
-      <c r="CT61" s="46" t="n"/>
+      <c r="CT61" s="46" t="n">
+        <v>0.1069</v>
+      </c>
       <c r="CU61" s="29" t="n">
         <v>0</v>
       </c>
@@ -32368,7 +32288,7 @@
         <v>2</v>
       </c>
       <c r="CY61" s="31" t="n">
-        <v>83</v>
+        <v>10896000</v>
       </c>
       <c r="CZ61" s="32" t="n">
         <v>4</v>
@@ -32377,6 +32297,76 @@
         <v>10</v>
       </c>
       <c r="DB61" s="45" t="n"/>
+      <c r="DC61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF61" s="46" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="DG61" s="46" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="DH61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL61" s="31" t="n"/>
+      <c r="DM61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="DN61" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="DO61" s="45" t="n"/>
+      <c r="DP61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ61" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="DR61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS61" s="46" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="DT61" s="46" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="DU61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY61" s="31" t="n"/>
+      <c r="DZ61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA61" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB61" s="45" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="14" t="inlineStr">
@@ -32723,10 +32713,10 @@
         <v>2</v>
       </c>
       <c r="DS62" s="43" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT62" s="43" t="n">
-        <v>0.1579</v>
+        <v>0.2692</v>
       </c>
       <c r="DU62" s="21" t="n">
         <v>0</v>
@@ -32745,7 +32735,7 @@
         <v>4</v>
       </c>
       <c r="EA62" s="21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB62" s="39" t="n"/>
     </row>
@@ -32886,10 +32876,10 @@
         <v>2</v>
       </c>
       <c r="DS63" s="46" t="n">
-        <v>0.3739</v>
+        <v>0.4126</v>
       </c>
       <c r="DT63" s="46" t="n">
-        <v>0.2317</v>
+        <v>0.2766</v>
       </c>
       <c r="DU63" s="29" t="n">
         <v>0</v>
@@ -32908,7 +32898,7 @@
         <v>4</v>
       </c>
       <c r="EA63" s="29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="EB63" s="45" t="n"/>
     </row>
@@ -33297,10 +33287,10 @@
         <v>2</v>
       </c>
       <c r="DS64" s="43" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT64" s="43" t="n">
-        <v>0.4722</v>
+        <v>0.5897</v>
       </c>
       <c r="DU64" s="21" t="n">
         <v>2</v>
@@ -33714,10 +33704,10 @@
         <v>2</v>
       </c>
       <c r="DS65" s="46" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT65" s="46" t="n">
-        <v>0.5231</v>
+        <v>0.4906</v>
       </c>
       <c r="DU65" s="29" t="n">
         <v>2</v>
@@ -34119,10 +34109,10 @@
         <v>2</v>
       </c>
       <c r="DS66" s="43" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT66" s="43" t="n">
-        <v>0.5238</v>
+        <v>0.4662</v>
       </c>
       <c r="DU66" s="21" t="n">
         <v>2</v>
@@ -34514,10 +34504,10 @@
         <v>2</v>
       </c>
       <c r="DS67" s="46" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT67" s="46" t="n">
-        <v>0.3607</v>
+        <v>0.3956</v>
       </c>
       <c r="DU67" s="29" t="n">
         <v>0</v>
@@ -34909,10 +34899,10 @@
         <v>2</v>
       </c>
       <c r="DS68" s="43" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT68" s="43" t="n">
-        <v>0.5625</v>
+        <v>0.5159</v>
       </c>
       <c r="DU68" s="21" t="n">
         <v>2</v>
@@ -35294,10 +35284,10 @@
         <v>2</v>
       </c>
       <c r="DS69" s="46" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT69" s="46" t="n">
-        <v>0.6167</v>
+        <v>0.5728</v>
       </c>
       <c r="DU69" s="29" t="n">
         <v>2</v>
@@ -35695,10 +35685,10 @@
         <v>2</v>
       </c>
       <c r="DS70" s="43" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT70" s="43" t="n">
-        <v>0.4353</v>
+        <v>0.3813</v>
       </c>
       <c r="DU70" s="21" t="n">
         <v>0</v>
@@ -36084,10 +36074,10 @@
         <v>2</v>
       </c>
       <c r="DS71" s="46" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT71" s="46" t="n">
-        <v>0.2973</v>
+        <v>0.3803</v>
       </c>
       <c r="DU71" s="29" t="n">
         <v>0</v>
@@ -36469,10 +36459,10 @@
         <v>2</v>
       </c>
       <c r="DS72" s="43" t="n">
-        <v>0.4519</v>
+        <v>0.4584</v>
       </c>
       <c r="DT72" s="43" t="n">
-        <v>0.2755</v>
+        <v>0.3333</v>
       </c>
       <c r="DU72" s="21" t="n">
         <v>0</v>
@@ -36880,10 +36870,10 @@
         <v>2</v>
       </c>
       <c r="DS73" s="46" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT73" s="46" t="n">
-        <v>0.5185</v>
+        <v>0.4904</v>
       </c>
       <c r="DU73" s="29" t="n">
         <v>0</v>
@@ -37287,10 +37277,10 @@
         <v>2</v>
       </c>
       <c r="DS74" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT74" s="43" t="n">
-        <v>0.5726</v>
+        <v>0.525</v>
       </c>
       <c r="DU74" s="21" t="n">
         <v>2</v>
@@ -37357,7 +37347,7 @@
         <v>18</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K75" s="17" t="n">
         <v>18</v>
@@ -37366,10 +37356,10 @@
         <v>109661425</v>
       </c>
       <c r="M75" s="41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N75" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O75" s="42" t="inlineStr">
         <is>
@@ -37700,13 +37690,13 @@
         <v>2</v>
       </c>
       <c r="DS75" s="46" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT75" s="46" t="n">
-        <v>0.5169</v>
+        <v>0.5401</v>
       </c>
       <c r="DU75" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV75" s="29" t="n">
         <v>0</v>
@@ -37719,12 +37709,16 @@
       </c>
       <c r="DY75" s="31" t="n"/>
       <c r="DZ75" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EA75" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="EB75" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="EB75" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="14" t="inlineStr">
@@ -38083,10 +38077,10 @@
         <v>2</v>
       </c>
       <c r="DS76" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT76" s="43" t="n">
-        <v>0.3204</v>
+        <v>0.3766</v>
       </c>
       <c r="DU76" s="21" t="n">
         <v>0</v>
@@ -38478,10 +38472,10 @@
         <v>2</v>
       </c>
       <c r="DS77" s="46" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT77" s="46" t="n">
-        <v>0.5135</v>
+        <v>0.4947</v>
       </c>
       <c r="DU77" s="29" t="n">
         <v>0</v>
@@ -38865,10 +38859,10 @@
         <v>2</v>
       </c>
       <c r="DS78" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT78" s="43" t="n">
-        <v>0.3962</v>
+        <v>0.4052</v>
       </c>
       <c r="DU78" s="21" t="n">
         <v>0</v>
@@ -39248,10 +39242,10 @@
         <v>2</v>
       </c>
       <c r="DS79" s="46" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT79" s="46" t="n">
-        <v>0.7358</v>
+        <v>0.7308</v>
       </c>
       <c r="DU79" s="29" t="n">
         <v>2</v>
@@ -39296,12 +39290,12 @@
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>71017</t>
+          <t>273031</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>Phạm Ngọc Tương</t>
+          <t>Đỗ Văn Thi</t>
         </is>
       </c>
       <c r="G80" s="39" t="inlineStr">
@@ -39315,22 +39309,22 @@
         </is>
       </c>
       <c r="I80" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K80" s="17" t="n">
         <v>16</v>
       </c>
       <c r="L80" s="40" t="n">
-        <v>97693569</v>
+        <v>59110823</v>
       </c>
       <c r="M80" s="41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N80" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O80" s="47" t="n"/>
       <c r="P80" s="21" t="n">
@@ -39378,9 +39372,7 @@
       <c r="AF80" s="43" t="n">
         <v>0.158</v>
       </c>
-      <c r="AG80" s="43" t="n">
-        <v>0.0238</v>
-      </c>
+      <c r="AG80" s="43" t="n"/>
       <c r="AH80" s="21" t="n">
         <v>0</v>
       </c>
@@ -39394,7 +39386,7 @@
         <v>2</v>
       </c>
       <c r="AL80" s="23" t="n">
-        <v>2631000</v>
+        <v>300</v>
       </c>
       <c r="AM80" s="24" t="n">
         <v>4</v>
@@ -39407,19 +39399,19 @@
         <v>0</v>
       </c>
       <c r="AQ80" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR80" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS80" s="43" t="n">
         <v>0.243</v>
       </c>
       <c r="AT80" s="43" t="n">
-        <v>0.2638</v>
+        <v>0.1402</v>
       </c>
       <c r="AU80" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV80" s="21" t="n">
         <v>0</v>
@@ -39431,7 +39423,7 @@
         <v>2</v>
       </c>
       <c r="AY80" s="23" t="n">
-        <v>20767000</v>
+        <v>12161000</v>
       </c>
       <c r="AZ80" s="24" t="n">
         <v>4</v>
@@ -39444,10 +39436,10 @@
         <v>0</v>
       </c>
       <c r="BD80" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE80" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF80" s="43" t="n">
         <v>0.3229</v>
@@ -39466,13 +39458,13 @@
         <v>2</v>
       </c>
       <c r="BL80" s="23" t="n">
-        <v>18360046</v>
+        <v>11211000</v>
       </c>
       <c r="BM80" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN80" s="21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BO80" s="39" t="n"/>
       <c r="BP80" s="21" t="n">
@@ -39488,7 +39480,7 @@
         <v>0.3482</v>
       </c>
       <c r="BT80" s="43" t="n">
-        <v>0.2575</v>
+        <v>0.2178</v>
       </c>
       <c r="BU80" s="21" t="n">
         <v>0</v>
@@ -39503,7 +39495,7 @@
         <v>2</v>
       </c>
       <c r="BY80" s="23" t="n">
-        <v>17956523</v>
+        <v>14146923</v>
       </c>
       <c r="BZ80" s="24" t="n">
         <v>4</v>
@@ -39516,16 +39508,16 @@
         <v>0</v>
       </c>
       <c r="CD80" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CE80" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF80" s="43" t="n">
         <v>0.2772</v>
       </c>
       <c r="CG80" s="43" t="n">
-        <v>0.2615</v>
+        <v>0.2563</v>
       </c>
       <c r="CH80" s="21" t="n">
         <v>0</v>
@@ -39540,13 +39532,13 @@
         <v>2</v>
       </c>
       <c r="CL80" s="23" t="n">
-        <v>18872000</v>
+        <v>10390000</v>
       </c>
       <c r="CM80" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CN80" s="21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CO80" s="39" t="n"/>
       <c r="CP80" s="21" t="n">
@@ -39562,7 +39554,7 @@
         <v>0.366</v>
       </c>
       <c r="CT80" s="43" t="n">
-        <v>0.3388</v>
+        <v>0.2473</v>
       </c>
       <c r="CU80" s="21" t="n">
         <v>0</v>
@@ -39577,7 +39569,7 @@
         <v>2</v>
       </c>
       <c r="CY80" s="23" t="n">
-        <v>19107000</v>
+        <v>11201600</v>
       </c>
       <c r="CZ80" s="24" t="n">
         <v>4</v>
@@ -39599,7 +39591,7 @@
         <v>0.4978</v>
       </c>
       <c r="DG80" s="43" t="n">
-        <v>0.4557</v>
+        <v>0.3333</v>
       </c>
       <c r="DH80" s="21" t="n">
         <v>0</v>
@@ -39631,13 +39623,13 @@
         <v>2</v>
       </c>
       <c r="DS80" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT80" s="43" t="n">
-        <v>0.5269</v>
+        <v>0.3565</v>
       </c>
       <c r="DU80" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV80" s="21" t="n">
         <v>0</v>
@@ -39650,16 +39642,12 @@
       </c>
       <c r="DY80" s="23" t="n"/>
       <c r="DZ80" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA80" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB80" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="EB80" s="39" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
@@ -39679,12 +39667,12 @@
       </c>
       <c r="E81" s="26" t="inlineStr">
         <is>
-          <t>273031</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>Đỗ Văn Thi</t>
+          <t>Phạm Ngọc Tương</t>
         </is>
       </c>
       <c r="G81" s="45" t="inlineStr">
@@ -39698,22 +39686,22 @@
         </is>
       </c>
       <c r="I81" s="17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K81" s="17" t="n">
         <v>16</v>
       </c>
       <c r="L81" s="40" t="n">
-        <v>59110823</v>
+        <v>97693569</v>
       </c>
       <c r="M81" s="41" t="n">
         <v>30</v>
       </c>
       <c r="N81" s="17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O81" s="47" t="n"/>
       <c r="P81" s="29" t="n">
@@ -39761,7 +39749,9 @@
       <c r="AF81" s="46" t="n">
         <v>0.158</v>
       </c>
-      <c r="AG81" s="46" t="n"/>
+      <c r="AG81" s="46" t="n">
+        <v>0.0238</v>
+      </c>
       <c r="AH81" s="29" t="n">
         <v>0</v>
       </c>
@@ -39775,7 +39765,7 @@
         <v>2</v>
       </c>
       <c r="AL81" s="31" t="n">
-        <v>300</v>
+        <v>2631000</v>
       </c>
       <c r="AM81" s="32" t="n">
         <v>4</v>
@@ -39788,19 +39778,19 @@
         <v>0</v>
       </c>
       <c r="AQ81" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR81" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS81" s="46" t="n">
         <v>0.243</v>
       </c>
       <c r="AT81" s="46" t="n">
-        <v>0.1402</v>
+        <v>0.2638</v>
       </c>
       <c r="AU81" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV81" s="29" t="n">
         <v>0</v>
@@ -39812,7 +39802,7 @@
         <v>2</v>
       </c>
       <c r="AY81" s="31" t="n">
-        <v>12161000</v>
+        <v>20767000</v>
       </c>
       <c r="AZ81" s="32" t="n">
         <v>4</v>
@@ -39825,10 +39815,10 @@
         <v>0</v>
       </c>
       <c r="BD81" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE81" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF81" s="46" t="n">
         <v>0.3229</v>
@@ -39847,13 +39837,13 @@
         <v>2</v>
       </c>
       <c r="BL81" s="31" t="n">
-        <v>11211000</v>
+        <v>18360046</v>
       </c>
       <c r="BM81" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN81" s="29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BO81" s="45" t="n"/>
       <c r="BP81" s="29" t="n">
@@ -39869,7 +39859,7 @@
         <v>0.3482</v>
       </c>
       <c r="BT81" s="46" t="n">
-        <v>0.2178</v>
+        <v>0.2575</v>
       </c>
       <c r="BU81" s="29" t="n">
         <v>0</v>
@@ -39884,7 +39874,7 @@
         <v>2</v>
       </c>
       <c r="BY81" s="31" t="n">
-        <v>14146923</v>
+        <v>17956523</v>
       </c>
       <c r="BZ81" s="32" t="n">
         <v>4</v>
@@ -39897,16 +39887,16 @@
         <v>0</v>
       </c>
       <c r="CD81" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE81" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF81" s="46" t="n">
         <v>0.2772</v>
       </c>
       <c r="CG81" s="46" t="n">
-        <v>0.2563</v>
+        <v>0.2615</v>
       </c>
       <c r="CH81" s="29" t="n">
         <v>0</v>
@@ -39921,13 +39911,13 @@
         <v>2</v>
       </c>
       <c r="CL81" s="31" t="n">
-        <v>10390000</v>
+        <v>18872000</v>
       </c>
       <c r="CM81" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CN81" s="29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CO81" s="45" t="n"/>
       <c r="CP81" s="29" t="n">
@@ -39943,7 +39933,7 @@
         <v>0.366</v>
       </c>
       <c r="CT81" s="46" t="n">
-        <v>0.2473</v>
+        <v>0.3388</v>
       </c>
       <c r="CU81" s="29" t="n">
         <v>0</v>
@@ -39958,7 +39948,7 @@
         <v>2</v>
       </c>
       <c r="CY81" s="31" t="n">
-        <v>11201600</v>
+        <v>19107000</v>
       </c>
       <c r="CZ81" s="32" t="n">
         <v>4</v>
@@ -39980,7 +39970,7 @@
         <v>0.4978</v>
       </c>
       <c r="DG81" s="46" t="n">
-        <v>0.3333</v>
+        <v>0.4557</v>
       </c>
       <c r="DH81" s="29" t="n">
         <v>0</v>
@@ -40012,10 +40002,10 @@
         <v>2</v>
       </c>
       <c r="DS81" s="46" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT81" s="46" t="n">
-        <v>0.4179</v>
+        <v>0.4671</v>
       </c>
       <c r="DU81" s="29" t="n">
         <v>0</v>
@@ -40387,10 +40377,10 @@
         <v>2</v>
       </c>
       <c r="DS82" s="43" t="n">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="DT82" s="43" t="n">
-        <v>0.6897</v>
+        <v>0.6239</v>
       </c>
       <c r="DU82" s="21" t="n">
         <v>2</v>
@@ -40800,10 +40790,10 @@
         <v>2</v>
       </c>
       <c r="DS83" s="46" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT83" s="46" t="n">
-        <v>0.4758</v>
+        <v>0.4714</v>
       </c>
       <c r="DU83" s="29" t="n">
         <v>2</v>
@@ -40870,7 +40860,7 @@
         <v>12</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K84" s="17" t="n">
         <v>18</v>
@@ -40879,7 +40869,7 @@
         <v>121946278</v>
       </c>
       <c r="M84" s="41" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N84" s="17" t="n">
         <v>2</v>
@@ -41213,13 +41203,13 @@
         <v>0</v>
       </c>
       <c r="DS84" s="43" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT84" s="43" t="n">
-        <v>0.2621</v>
+        <v>0.3246</v>
       </c>
       <c r="DU84" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV84" s="21" t="n">
         <v>0</v>
@@ -41232,10 +41222,10 @@
       </c>
       <c r="DY84" s="23" t="n"/>
       <c r="DZ84" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EA84" s="21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="EB84" s="39" t="n"/>
     </row>
@@ -41276,7 +41266,7 @@
         </is>
       </c>
       <c r="I85" s="17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J85" s="17" t="n">
         <v>8</v>
@@ -41288,10 +41278,10 @@
         <v>83086893</v>
       </c>
       <c r="M85" s="41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N85" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O85" s="47" t="n"/>
       <c r="P85" s="29" t="n">
@@ -41602,13 +41592,13 @@
         <v>0</v>
       </c>
       <c r="DQ85" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR85" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS85" s="46" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT85" s="46" t="n">
         <v>0.1667</v>
@@ -41627,10 +41617,10 @@
       </c>
       <c r="DY85" s="31" t="n"/>
       <c r="DZ85" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EA85" s="29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="EB85" s="45" t="n"/>
     </row>
@@ -41993,10 +41983,10 @@
         <v>2</v>
       </c>
       <c r="DS86" s="43" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT86" s="43" t="n">
-        <v>0.3103</v>
+        <v>0.3113</v>
       </c>
       <c r="DU86" s="21" t="n">
         <v>2</v>
@@ -42063,7 +42053,7 @@
         <v>16</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K87" s="17" t="n">
         <v>14</v>
@@ -42072,7 +42062,7 @@
         <v>52529033</v>
       </c>
       <c r="M87" s="41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N87" s="17" t="n">
         <v>5</v>
@@ -42376,13 +42366,13 @@
         <v>2</v>
       </c>
       <c r="DS87" s="46" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT87" s="46" t="n">
-        <v>0.2115</v>
+        <v>0.3093</v>
       </c>
       <c r="DU87" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV87" s="29" t="n">
         <v>0</v>
@@ -42395,12 +42385,16 @@
       </c>
       <c r="DY87" s="31" t="n"/>
       <c r="DZ87" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EA87" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="EB87" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="EB87" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="14" t="inlineStr">
@@ -42454,7 +42448,7 @@
         <v>30</v>
       </c>
       <c r="N88" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O88" s="47" t="n"/>
       <c r="P88" s="21" t="n">
@@ -42761,10 +42755,10 @@
         <v>2</v>
       </c>
       <c r="DS88" s="43" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT88" s="43" t="n">
-        <v>0.0968</v>
+        <v>0.1905</v>
       </c>
       <c r="DU88" s="21" t="n">
         <v>0</v>
@@ -42783,7 +42777,7 @@
         <v>4</v>
       </c>
       <c r="EA88" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="EB88" s="39" t="n"/>
     </row>
@@ -42996,10 +42990,10 @@
         <v>2</v>
       </c>
       <c r="DS89" s="46" t="n">
-        <v>0.2681</v>
+        <v>0.3058</v>
       </c>
       <c r="DT89" s="46" t="n">
-        <v>0.3535</v>
+        <v>0.3671</v>
       </c>
       <c r="DU89" s="29" t="n">
         <v>2</v>
@@ -43066,7 +43060,7 @@
         <v>18</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K90" s="17" t="n">
         <v>18</v>
@@ -43075,16 +43069,12 @@
         <v>92986927</v>
       </c>
       <c r="M90" s="41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N90" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="O90" s="42" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+      <c r="O90" s="47" t="n"/>
       <c r="P90" s="21" t="n">
         <v>0</v>
       </c>
@@ -43409,13 +43399,13 @@
         <v>2</v>
       </c>
       <c r="DS90" s="43" t="n">
-        <v>0.4897</v>
+        <v>0.4139</v>
       </c>
       <c r="DT90" s="43" t="n">
-        <v>0.5775</v>
+        <v>0.3816</v>
       </c>
       <c r="DU90" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV90" s="21" t="n">
         <v>0</v>
@@ -43428,16 +43418,12 @@
       </c>
       <c r="DY90" s="23" t="n"/>
       <c r="DZ90" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA90" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB90" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="EB90" s="39" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
@@ -43491,9 +43477,13 @@
         <v>46</v>
       </c>
       <c r="N91" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" s="47" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O91" s="42" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="P91" s="29" t="n">
         <v>0</v>
       </c>
@@ -43814,10 +43804,10 @@
         <v>2</v>
       </c>
       <c r="DS91" s="46" t="n">
-        <v>0.4897</v>
+        <v>0.4139</v>
       </c>
       <c r="DT91" s="46" t="n">
-        <v>0.4324</v>
+        <v>0.395</v>
       </c>
       <c r="DU91" s="29" t="n">
         <v>0</v>
@@ -43836,7 +43826,7 @@
         <v>4</v>
       </c>
       <c r="EA91" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EB91" s="45" t="n"/>
     </row>
@@ -44203,7 +44193,7 @@
         <v>2</v>
       </c>
       <c r="DS92" s="43" t="n">
-        <v>0.4897</v>
+        <v>0.4139</v>
       </c>
       <c r="DT92" s="43" t="n">
         <v>0.5294</v>
@@ -44592,10 +44582,10 @@
         <v>2</v>
       </c>
       <c r="DS93" s="46" t="n">
-        <v>0.4897</v>
+        <v>0.4139</v>
       </c>
       <c r="DT93" s="46" t="n">
-        <v>0.4194</v>
+        <v>0.3496</v>
       </c>
       <c r="DU93" s="29" t="n">
         <v>0</v>
@@ -44614,7 +44604,7 @@
         <v>4</v>
       </c>
       <c r="EA93" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EB93" s="45" t="n"/>
     </row>
@@ -44993,10 +44983,10 @@
         <v>2</v>
       </c>
       <c r="DS94" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT94" s="43" t="n">
-        <v>0.4038</v>
+        <v>0.4021</v>
       </c>
       <c r="DU94" s="21" t="n">
         <v>2</v>
@@ -45408,10 +45398,10 @@
         <v>2</v>
       </c>
       <c r="DS95" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT95" s="46" t="n">
-        <v>0.4574</v>
+        <v>0.4182</v>
       </c>
       <c r="DU95" s="29" t="n">
         <v>2</v>
@@ -45815,10 +45805,10 @@
         <v>2</v>
       </c>
       <c r="DS96" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT96" s="43" t="n">
-        <v>0.411</v>
+        <v>0.4123</v>
       </c>
       <c r="DU96" s="21" t="n">
         <v>2</v>
@@ -46218,10 +46208,10 @@
         <v>2</v>
       </c>
       <c r="DS97" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT97" s="46" t="n">
-        <v>0.4426</v>
+        <v>0.4712</v>
       </c>
       <c r="DU97" s="29" t="n">
         <v>2</v>
@@ -46266,12 +46256,12 @@
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>80263</t>
+          <t>79982</t>
         </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Văn Hoàng</t>
         </is>
       </c>
       <c r="G98" s="39" t="inlineStr">
@@ -46285,16 +46275,16 @@
         </is>
       </c>
       <c r="I98" s="17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K98" s="17" t="n">
         <v>18</v>
       </c>
       <c r="L98" s="40" t="n">
-        <v>103894310</v>
+        <v>109416939</v>
       </c>
       <c r="M98" s="41" t="n">
         <v>48</v>
@@ -46320,10 +46310,10 @@
         <v>0.2256</v>
       </c>
       <c r="T98" s="43" t="n">
-        <v>0.204</v>
+        <v>0.275</v>
       </c>
       <c r="U98" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V98" s="21" t="n">
         <v>0</v>
@@ -46335,29 +46325,33 @@
         <v>2</v>
       </c>
       <c r="Y98" s="23" t="n">
-        <v>13089070</v>
+        <v>14877370</v>
       </c>
       <c r="Z98" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA98" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB98" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AB98" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="AC98" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AD98" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE98" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF98" s="43" t="n">
         <v>0.1549</v>
       </c>
       <c r="AG98" s="43" t="n">
-        <v>0.1152</v>
+        <v>0.1026</v>
       </c>
       <c r="AH98" s="21" t="n">
         <v>0</v>
@@ -46372,13 +46366,13 @@
         <v>2</v>
       </c>
       <c r="AL98" s="23" t="n">
-        <v>13778017</v>
+        <v>12822300</v>
       </c>
       <c r="AM98" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN98" s="21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AO98" s="39" t="n"/>
       <c r="AP98" s="21" t="n">
@@ -46394,7 +46388,7 @@
         <v>0.1845</v>
       </c>
       <c r="AT98" s="43" t="n">
-        <v>0.1441</v>
+        <v>0.1356</v>
       </c>
       <c r="AU98" s="21" t="n">
         <v>0</v>
@@ -46409,7 +46403,7 @@
         <v>2</v>
       </c>
       <c r="AY98" s="23" t="n">
-        <v>17249023</v>
+        <v>17597046</v>
       </c>
       <c r="AZ98" s="24" t="n">
         <v>4</v>
@@ -46431,7 +46425,7 @@
         <v>0.393</v>
       </c>
       <c r="BG98" s="43" t="n">
-        <v>0.5057</v>
+        <v>0.4392</v>
       </c>
       <c r="BH98" s="21" t="n">
         <v>2</v>
@@ -46446,7 +46440,7 @@
         <v>2</v>
       </c>
       <c r="BL98" s="23" t="n">
-        <v>12653769</v>
+        <v>16381692</v>
       </c>
       <c r="BM98" s="24" t="n">
         <v>6</v>
@@ -46472,7 +46466,7 @@
         <v>0.3139</v>
       </c>
       <c r="BT98" s="43" t="n">
-        <v>0.4242</v>
+        <v>0.4196</v>
       </c>
       <c r="BU98" s="21" t="n">
         <v>2</v>
@@ -46487,7 +46481,7 @@
         <v>2</v>
       </c>
       <c r="BY98" s="23" t="n">
-        <v>19350846</v>
+        <v>18084346</v>
       </c>
       <c r="BZ98" s="24" t="n">
         <v>6</v>
@@ -46513,7 +46507,7 @@
         <v>0.2929</v>
       </c>
       <c r="CG98" s="43" t="n">
-        <v>0.4014</v>
+        <v>0.3896</v>
       </c>
       <c r="CH98" s="21" t="n">
         <v>2</v>
@@ -46528,7 +46522,7 @@
         <v>2</v>
       </c>
       <c r="CL98" s="23" t="n">
-        <v>14580400</v>
+        <v>16444000</v>
       </c>
       <c r="CM98" s="24" t="n">
         <v>6</v>
@@ -46554,7 +46548,7 @@
         <v>0.3638</v>
       </c>
       <c r="CT98" s="43" t="n">
-        <v>0.437</v>
+        <v>0.3642</v>
       </c>
       <c r="CU98" s="21" t="n">
         <v>2</v>
@@ -46569,7 +46563,7 @@
         <v>2</v>
       </c>
       <c r="CY98" s="23" t="n">
-        <v>13193185</v>
+        <v>13210185</v>
       </c>
       <c r="CZ98" s="24" t="n">
         <v>6</v>
@@ -46595,7 +46589,7 @@
         <v>0.3345</v>
       </c>
       <c r="DG98" s="43" t="n">
-        <v>0.4189</v>
+        <v>0.3468</v>
       </c>
       <c r="DH98" s="21" t="n">
         <v>2</v>
@@ -46631,10 +46625,10 @@
         <v>2</v>
       </c>
       <c r="DS98" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT98" s="43" t="n">
-        <v>0.4107</v>
+        <v>0.3409</v>
       </c>
       <c r="DU98" s="21" t="n">
         <v>2</v>
@@ -46679,12 +46673,12 @@
       </c>
       <c r="E99" s="26" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>80263</t>
         </is>
       </c>
       <c r="F99" s="27" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Hoàng</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="G99" s="45" t="inlineStr">
@@ -46707,7 +46701,7 @@
         <v>18</v>
       </c>
       <c r="L99" s="40" t="n">
-        <v>109416939</v>
+        <v>103894310</v>
       </c>
       <c r="M99" s="41" t="n">
         <v>46</v>
@@ -46729,10 +46723,10 @@
         <v>0.2256</v>
       </c>
       <c r="T99" s="46" t="n">
-        <v>0.275</v>
+        <v>0.204</v>
       </c>
       <c r="U99" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V99" s="29" t="n">
         <v>0</v>
@@ -46744,33 +46738,29 @@
         <v>2</v>
       </c>
       <c r="Y99" s="31" t="n">
-        <v>14877370</v>
+        <v>13089070</v>
       </c>
       <c r="Z99" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA99" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AB99" s="45" t="n"/>
       <c r="AC99" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AD99" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE99" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF99" s="46" t="n">
         <v>0.1549</v>
       </c>
       <c r="AG99" s="46" t="n">
-        <v>0.1026</v>
+        <v>0.1152</v>
       </c>
       <c r="AH99" s="29" t="n">
         <v>0</v>
@@ -46785,13 +46775,13 @@
         <v>2</v>
       </c>
       <c r="AL99" s="31" t="n">
-        <v>12822300</v>
+        <v>13778017</v>
       </c>
       <c r="AM99" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN99" s="29" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AO99" s="45" t="n"/>
       <c r="AP99" s="29" t="n">
@@ -46807,7 +46797,7 @@
         <v>0.1845</v>
       </c>
       <c r="AT99" s="46" t="n">
-        <v>0.1356</v>
+        <v>0.1441</v>
       </c>
       <c r="AU99" s="29" t="n">
         <v>0</v>
@@ -46822,7 +46812,7 @@
         <v>2</v>
       </c>
       <c r="AY99" s="31" t="n">
-        <v>17597046</v>
+        <v>17249023</v>
       </c>
       <c r="AZ99" s="32" t="n">
         <v>4</v>
@@ -46844,7 +46834,7 @@
         <v>0.393</v>
       </c>
       <c r="BG99" s="46" t="n">
-        <v>0.4392</v>
+        <v>0.5057</v>
       </c>
       <c r="BH99" s="29" t="n">
         <v>2</v>
@@ -46859,7 +46849,7 @@
         <v>2</v>
       </c>
       <c r="BL99" s="31" t="n">
-        <v>16381692</v>
+        <v>12653769</v>
       </c>
       <c r="BM99" s="32" t="n">
         <v>6</v>
@@ -46885,7 +46875,7 @@
         <v>0.3139</v>
       </c>
       <c r="BT99" s="46" t="n">
-        <v>0.4196</v>
+        <v>0.4242</v>
       </c>
       <c r="BU99" s="29" t="n">
         <v>2</v>
@@ -46900,7 +46890,7 @@
         <v>2</v>
       </c>
       <c r="BY99" s="31" t="n">
-        <v>18084346</v>
+        <v>19350846</v>
       </c>
       <c r="BZ99" s="32" t="n">
         <v>6</v>
@@ -46926,7 +46916,7 @@
         <v>0.2929</v>
       </c>
       <c r="CG99" s="46" t="n">
-        <v>0.3896</v>
+        <v>0.4014</v>
       </c>
       <c r="CH99" s="29" t="n">
         <v>2</v>
@@ -46941,7 +46931,7 @@
         <v>2</v>
       </c>
       <c r="CL99" s="31" t="n">
-        <v>16444000</v>
+        <v>14580400</v>
       </c>
       <c r="CM99" s="32" t="n">
         <v>6</v>
@@ -46967,7 +46957,7 @@
         <v>0.3638</v>
       </c>
       <c r="CT99" s="46" t="n">
-        <v>0.3642</v>
+        <v>0.437</v>
       </c>
       <c r="CU99" s="29" t="n">
         <v>2</v>
@@ -46982,7 +46972,7 @@
         <v>2</v>
       </c>
       <c r="CY99" s="31" t="n">
-        <v>13210185</v>
+        <v>13193185</v>
       </c>
       <c r="CZ99" s="32" t="n">
         <v>6</v>
@@ -47008,7 +46998,7 @@
         <v>0.3345</v>
       </c>
       <c r="DG99" s="46" t="n">
-        <v>0.3468</v>
+        <v>0.4189</v>
       </c>
       <c r="DH99" s="29" t="n">
         <v>2</v>
@@ -47038,19 +47028,19 @@
         <v>0</v>
       </c>
       <c r="DQ99" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR99" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS99" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT99" s="46" t="n">
-        <v>0.3086</v>
+        <v>0.425</v>
       </c>
       <c r="DU99" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV99" s="29" t="n">
         <v>0</v>
@@ -47066,7 +47056,7 @@
         <v>4</v>
       </c>
       <c r="EA99" s="29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB99" s="45" t="n"/>
     </row>
@@ -47437,10 +47427,10 @@
         <v>2</v>
       </c>
       <c r="DS100" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT100" s="43" t="n">
-        <v>0.4186</v>
+        <v>0.3816</v>
       </c>
       <c r="DU100" s="21" t="n">
         <v>2</v>
@@ -47842,10 +47832,10 @@
         <v>2</v>
       </c>
       <c r="DS101" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT101" s="46" t="n">
-        <v>0.1818</v>
+        <v>0.2768</v>
       </c>
       <c r="DU101" s="29" t="n">
         <v>0</v>
@@ -47864,7 +47854,7 @@
         <v>4</v>
       </c>
       <c r="EA101" s="29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB101" s="45" t="n"/>
     </row>
@@ -48239,10 +48229,10 @@
         <v>2</v>
       </c>
       <c r="DS102" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT102" s="43" t="n">
-        <v>0.1429</v>
+        <v>0.1944</v>
       </c>
       <c r="DU102" s="21" t="n">
         <v>0</v>
@@ -48261,7 +48251,7 @@
         <v>4</v>
       </c>
       <c r="EA102" s="21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB102" s="39" t="n"/>
     </row>
@@ -48622,10 +48612,10 @@
         <v>2</v>
       </c>
       <c r="DS103" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT103" s="46" t="n">
-        <v>0.3797</v>
+        <v>0.4141</v>
       </c>
       <c r="DU103" s="29" t="n">
         <v>2</v>
@@ -49015,10 +49005,10 @@
         <v>2</v>
       </c>
       <c r="DS104" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT104" s="43" t="n">
-        <v>0.1129</v>
+        <v>0.1613</v>
       </c>
       <c r="DU104" s="21" t="n">
         <v>0</v>
@@ -49037,7 +49027,7 @@
         <v>4</v>
       </c>
       <c r="EA104" s="21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB104" s="39" t="n"/>
     </row>
@@ -49398,10 +49388,10 @@
         <v>2</v>
       </c>
       <c r="DS105" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT105" s="46" t="n">
-        <v>0.0781</v>
+        <v>0.0741</v>
       </c>
       <c r="DU105" s="29" t="n">
         <v>0</v>
@@ -49420,7 +49410,7 @@
         <v>4</v>
       </c>
       <c r="EA105" s="29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB105" s="45" t="n"/>
     </row>
@@ -49777,10 +49767,10 @@
         <v>2</v>
       </c>
       <c r="DS106" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT106" s="43" t="n">
-        <v>0.1429</v>
+        <v>0.1402</v>
       </c>
       <c r="DU106" s="21" t="n">
         <v>0</v>
@@ -49799,7 +49789,7 @@
         <v>4</v>
       </c>
       <c r="EA106" s="21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB106" s="39" t="n"/>
     </row>
@@ -50162,10 +50152,10 @@
         <v>2</v>
       </c>
       <c r="DS107" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT107" s="46" t="n">
-        <v>0.47</v>
+        <v>0.435</v>
       </c>
       <c r="DU107" s="29" t="n">
         <v>2</v>
@@ -50232,7 +50222,7 @@
         <v>10</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K108" s="17" t="n">
         <v>12</v>
@@ -50241,7 +50231,7 @@
         <v>25991340</v>
       </c>
       <c r="M108" s="41" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N108" s="17" t="n">
         <v>15</v>
@@ -50537,13 +50527,13 @@
         <v>2</v>
       </c>
       <c r="DS108" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT108" s="43" t="n">
-        <v>0.3261</v>
+        <v>0.3176</v>
       </c>
       <c r="DU108" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV108" s="21" t="n">
         <v>0</v>
@@ -50556,16 +50546,12 @@
       </c>
       <c r="DY108" s="23" t="n"/>
       <c r="DZ108" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA108" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB108" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="EB108" s="39" t="n"/>
     </row>
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
@@ -50669,10 +50655,10 @@
         <v>2</v>
       </c>
       <c r="DS109" s="46" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT109" s="46" t="n">
-        <v>0.4118</v>
+        <v>0.4132</v>
       </c>
       <c r="DU109" s="29" t="n">
         <v>2</v>
@@ -50797,10 +50783,10 @@
         <v>2</v>
       </c>
       <c r="DS110" s="43" t="n">
-        <v>0.3146</v>
+        <v>0.329</v>
       </c>
       <c r="DT110" s="43" t="n">
-        <v>0.25</v>
+        <v>0.3143</v>
       </c>
       <c r="DU110" s="21" t="n">
         <v>0</v>
@@ -50819,7 +50805,7 @@
         <v>4</v>
       </c>
       <c r="EA110" s="21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="EB110" s="39" t="n"/>
     </row>
@@ -50863,7 +50849,7 @@
         <v>18</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K111" s="17" t="n">
         <v>18</v>
@@ -50872,7 +50858,7 @@
         <v>69370526</v>
       </c>
       <c r="M111" s="41" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N111" s="17" t="n">
         <v>1</v>
@@ -51214,13 +51200,13 @@
         <v>2</v>
       </c>
       <c r="DS111" s="46" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT111" s="46" t="n">
-        <v>0.3721</v>
+        <v>0.4222</v>
       </c>
       <c r="DU111" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV111" s="29" t="n">
         <v>0</v>
@@ -51233,12 +51219,16 @@
       </c>
       <c r="DY111" s="31" t="n"/>
       <c r="DZ111" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EA111" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="EB111" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="EB111" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="14" t="inlineStr">
@@ -51280,7 +51270,7 @@
         <v>18</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K112" s="17" t="n">
         <v>18</v>
@@ -51289,7 +51279,7 @@
         <v>73725126</v>
       </c>
       <c r="M112" s="41" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N112" s="17" t="n">
         <v>2</v>
@@ -51631,13 +51621,13 @@
         <v>2</v>
       </c>
       <c r="DS112" s="43" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT112" s="43" t="n">
-        <v>0.4179</v>
+        <v>0.4513</v>
       </c>
       <c r="DU112" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DV112" s="21" t="n">
         <v>0</v>
@@ -51650,12 +51640,16 @@
       </c>
       <c r="DY112" s="23" t="n"/>
       <c r="DZ112" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EA112" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="EB112" s="39" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="EB112" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
@@ -52032,10 +52026,10 @@
         <v>2</v>
       </c>
       <c r="DS113" s="46" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT113" s="46" t="n">
-        <v>0.5067</v>
+        <v>0.5455</v>
       </c>
       <c r="DU113" s="29" t="n">
         <v>2</v>
@@ -52437,10 +52431,10 @@
         <v>2</v>
       </c>
       <c r="DS114" s="43" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT114" s="43" t="n">
-        <v>0.4896</v>
+        <v>0.518</v>
       </c>
       <c r="DU114" s="21" t="n">
         <v>2</v>
@@ -52834,10 +52828,10 @@
         <v>2</v>
       </c>
       <c r="DS115" s="46" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT115" s="46" t="n">
-        <v>0.3667</v>
+        <v>0.36</v>
       </c>
       <c r="DU115" s="29" t="n">
         <v>0</v>
@@ -53223,10 +53217,10 @@
         <v>2</v>
       </c>
       <c r="DS116" s="43" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT116" s="43" t="n">
-        <v>0.3438</v>
+        <v>0.381</v>
       </c>
       <c r="DU116" s="21" t="n">
         <v>0</v>
@@ -53608,10 +53602,10 @@
         <v>2</v>
       </c>
       <c r="DS117" s="46" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT117" s="46" t="n">
-        <v>0.2632</v>
+        <v>0.2941</v>
       </c>
       <c r="DU117" s="29" t="n">
         <v>0</v>
@@ -53674,7 +53668,7 @@
         <v>14</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K118" s="17" t="n">
         <v>14</v>
@@ -53683,7 +53677,7 @@
         <v>47278800</v>
       </c>
       <c r="M118" s="41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N118" s="17" t="n">
         <v>8</v>
@@ -53989,13 +53983,13 @@
         <v>2</v>
       </c>
       <c r="DS118" s="43" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT118" s="43" t="n">
-        <v>0.4655</v>
+        <v>0.3933</v>
       </c>
       <c r="DU118" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV118" s="21" t="n">
         <v>0</v>
@@ -54008,16 +54002,12 @@
       </c>
       <c r="DY118" s="23" t="n"/>
       <c r="DZ118" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA118" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB118" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="EB118" s="39" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
@@ -54059,7 +54049,7 @@
         <v>12</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K119" s="17" t="n">
         <v>12</v>
@@ -54068,7 +54058,7 @@
         <v>17893700</v>
       </c>
       <c r="M119" s="41" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N119" s="17" t="n">
         <v>9</v>
@@ -54362,13 +54352,13 @@
         <v>2</v>
       </c>
       <c r="DS119" s="46" t="n">
-        <v>0.4288</v>
+        <v>0.4193</v>
       </c>
       <c r="DT119" s="46" t="n">
-        <v>0.6341</v>
+        <v>0.4079</v>
       </c>
       <c r="DU119" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV119" s="29" t="n">
         <v>0</v>
@@ -54381,16 +54371,12 @@
       </c>
       <c r="DY119" s="31" t="n"/>
       <c r="DZ119" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA119" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB119" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="EB119" s="45" t="n"/>
     </row>
     <row r="120">
       <c r="B120" s="14" t="inlineStr">
@@ -54429,7 +54415,7 @@
         </is>
       </c>
       <c r="I120" s="17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J120" s="17" t="n">
         <v>14</v>
@@ -54441,7 +54427,7 @@
         <v>84497171</v>
       </c>
       <c r="M120" s="41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N120" s="17" t="n">
         <v>1</v>
@@ -54777,16 +54763,16 @@
         <v>0</v>
       </c>
       <c r="DQ120" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS120" s="43" t="n">
-        <v>0.3332</v>
+        <v>0.3703</v>
       </c>
       <c r="DT120" s="43" t="n">
-        <v>0.2874</v>
+        <v>0.2822</v>
       </c>
       <c r="DU120" s="21" t="n">
         <v>0</v>
@@ -54802,10 +54788,10 @@
       </c>
       <c r="DY120" s="23" t="n"/>
       <c r="DZ120" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EA120" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="EB120" s="39" t="n"/>
     </row>
@@ -55176,10 +55162,10 @@
         <v>2</v>
       </c>
       <c r="DS121" s="46" t="n">
-        <v>0.3332</v>
+        <v>0.3703</v>
       </c>
       <c r="DT121" s="46" t="n">
-        <v>0.3654</v>
+        <v>0.3918</v>
       </c>
       <c r="DU121" s="29" t="n">
         <v>2</v>
@@ -55561,10 +55547,10 @@
         <v>2</v>
       </c>
       <c r="DS122" s="43" t="n">
-        <v>0.3332</v>
+        <v>0.3703</v>
       </c>
       <c r="DT122" s="43" t="n">
-        <v>0.3684</v>
+        <v>0.4059</v>
       </c>
       <c r="DU122" s="21" t="n">
         <v>2</v>
@@ -55944,10 +55930,10 @@
         <v>2</v>
       </c>
       <c r="DS123" s="46" t="n">
-        <v>0.3332</v>
+        <v>0.3703</v>
       </c>
       <c r="DT123" s="46" t="n">
-        <v>0.2405</v>
+        <v>0.2857</v>
       </c>
       <c r="DU123" s="29" t="n">
         <v>0</v>
@@ -56144,10 +56130,10 @@
         <v>2</v>
       </c>
       <c r="DS124" s="43" t="n">
-        <v>0.3332</v>
+        <v>0.3703</v>
       </c>
       <c r="DT124" s="43" t="n">
-        <v>0.4043</v>
+        <v>0.486</v>
       </c>
       <c r="DU124" s="21" t="n">
         <v>2</v>
@@ -56679,10 +56665,10 @@
         <v>2</v>
       </c>
       <c r="DS126" s="43" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT126" s="43" t="n">
-        <v>0.5455</v>
+        <v>0.5043</v>
       </c>
       <c r="DU126" s="21" t="n">
         <v>2</v>
@@ -57088,10 +57074,10 @@
         <v>2</v>
       </c>
       <c r="DS127" s="46" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT127" s="46" t="n">
-        <v>0.2396</v>
+        <v>0.2465</v>
       </c>
       <c r="DU127" s="29" t="n">
         <v>0</v>
@@ -57110,7 +57096,7 @@
         <v>4</v>
       </c>
       <c r="EA127" s="29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="EB127" s="45" t="n"/>
     </row>
@@ -57477,10 +57463,10 @@
         <v>2</v>
       </c>
       <c r="DS128" s="43" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT128" s="43" t="n">
-        <v>0.6269</v>
+        <v>0.6311</v>
       </c>
       <c r="DU128" s="21" t="n">
         <v>2</v>
@@ -57876,10 +57862,10 @@
         <v>2</v>
       </c>
       <c r="DS129" s="46" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT129" s="46" t="n">
-        <v>0.3038</v>
+        <v>0.331</v>
       </c>
       <c r="DU129" s="29" t="n">
         <v>0</v>
@@ -57898,7 +57884,7 @@
         <v>4</v>
       </c>
       <c r="EA129" s="29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="EB129" s="45" t="n"/>
     </row>
@@ -57939,7 +57925,7 @@
         </is>
       </c>
       <c r="I130" s="17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J130" s="17" t="n">
         <v>6</v>
@@ -57951,7 +57937,7 @@
         <v>122174727</v>
       </c>
       <c r="M130" s="41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N130" s="17" t="n">
         <v>5</v>
@@ -58263,16 +58249,16 @@
         <v>0</v>
       </c>
       <c r="DQ130" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR130" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS130" s="43" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT130" s="43" t="n">
-        <v>0.4</v>
+        <v>0.3841</v>
       </c>
       <c r="DU130" s="21" t="n">
         <v>2</v>
@@ -58288,16 +58274,12 @@
       </c>
       <c r="DY130" s="23" t="n"/>
       <c r="DZ130" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA130" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB130" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="EB130" s="39" t="n"/>
     </row>
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
@@ -58317,12 +58299,12 @@
       </c>
       <c r="E131" s="26" t="inlineStr">
         <is>
-          <t>101603</t>
+          <t>147258</t>
         </is>
       </c>
       <c r="F131" s="27" t="inlineStr">
         <is>
-          <t>Trần Minh Trung</t>
+          <t>Nguyễn Bá Mười</t>
         </is>
       </c>
       <c r="G131" s="45" t="inlineStr">
@@ -58336,19 +58318,19 @@
         </is>
       </c>
       <c r="I131" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J131" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K131" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="J131" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K131" s="17" t="n">
-        <v>18</v>
-      </c>
       <c r="L131" s="40" t="n">
-        <v>118018371</v>
+        <v>114226273</v>
       </c>
       <c r="M131" s="41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N131" s="17" t="n">
         <v>6</v>
@@ -58358,53 +58340,53 @@
         <v>0</v>
       </c>
       <c r="Q131" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S131" s="46" t="n">
         <v>0.1041</v>
       </c>
       <c r="T131" s="46" t="n">
-        <v>0.0673</v>
+        <v>0.1156</v>
       </c>
       <c r="U131" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V131" s="29" t="n">
         <v>0</v>
       </c>
       <c r="W131" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y131" s="31" t="n">
-        <v>12832185</v>
+        <v>15856241</v>
       </c>
       <c r="Z131" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA131" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB131" s="45" t="n"/>
       <c r="AC131" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AD131" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF131" s="46" t="n">
         <v>0.1179</v>
       </c>
       <c r="AG131" s="46" t="n">
-        <v>0.0876</v>
+        <v>0.04</v>
       </c>
       <c r="AH131" s="29" t="n">
         <v>0</v>
@@ -58419,13 +58401,13 @@
         <v>2</v>
       </c>
       <c r="AL131" s="31" t="n">
-        <v>13233417</v>
+        <v>11254417</v>
       </c>
       <c r="AM131" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN131" s="29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO131" s="45" t="n"/>
       <c r="AP131" s="29" t="n">
@@ -58441,7 +58423,7 @@
         <v>0.2487</v>
       </c>
       <c r="AT131" s="46" t="n">
-        <v>0.2014</v>
+        <v>0.1386</v>
       </c>
       <c r="AU131" s="29" t="n">
         <v>0</v>
@@ -58456,7 +58438,7 @@
         <v>2</v>
       </c>
       <c r="AY131" s="31" t="n">
-        <v>17834000</v>
+        <v>15828923</v>
       </c>
       <c r="AZ131" s="32" t="n">
         <v>4</v>
@@ -58491,7 +58473,7 @@
         <v>2</v>
       </c>
       <c r="BL131" s="31" t="n">
-        <v>18120846</v>
+        <v>13872846</v>
       </c>
       <c r="BM131" s="32" t="n">
         <v>4</v>
@@ -58513,7 +58495,7 @@
         <v>0.319</v>
       </c>
       <c r="BT131" s="46" t="n">
-        <v>0.2866</v>
+        <v>0.2535</v>
       </c>
       <c r="BU131" s="29" t="n">
         <v>0</v>
@@ -58528,7 +58510,7 @@
         <v>2</v>
       </c>
       <c r="BY131" s="31" t="n">
-        <v>18926923</v>
+        <v>16930846</v>
       </c>
       <c r="BZ131" s="32" t="n">
         <v>4</v>
@@ -58550,10 +58532,10 @@
         <v>0.1479</v>
       </c>
       <c r="CG131" s="46" t="n">
-        <v>0.0625</v>
+        <v>0.1717</v>
       </c>
       <c r="CH131" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CI131" s="29" t="n">
         <v>0</v>
@@ -58565,15 +58547,19 @@
         <v>2</v>
       </c>
       <c r="CL131" s="31" t="n">
-        <v>19333000</v>
+        <v>20988000</v>
       </c>
       <c r="CM131" s="32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN131" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="CO131" s="45" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="CO131" s="44" t="inlineStr">
+        <is>
+          <t>VƯỢT TRỘI</t>
+        </is>
+      </c>
       <c r="CP131" s="29" t="n">
         <v>0</v>
       </c>
@@ -58587,7 +58573,7 @@
         <v>0.3234</v>
       </c>
       <c r="CT131" s="46" t="n">
-        <v>0.2263</v>
+        <v>0.2049</v>
       </c>
       <c r="CU131" s="29" t="n">
         <v>0</v>
@@ -58602,7 +58588,7 @@
         <v>2</v>
       </c>
       <c r="CY131" s="31" t="n">
-        <v>17738000</v>
+        <v>19495000</v>
       </c>
       <c r="CZ131" s="32" t="n">
         <v>4</v>
@@ -58615,16 +58601,16 @@
         <v>0</v>
       </c>
       <c r="DD131" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE131" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DF131" s="46" t="n">
         <v>0.303</v>
       </c>
       <c r="DG131" s="46" t="n">
-        <v>0.2289</v>
+        <v>0.2143</v>
       </c>
       <c r="DH131" s="29" t="n">
         <v>0</v>
@@ -58640,10 +58626,10 @@
       </c>
       <c r="DL131" s="31" t="n"/>
       <c r="DM131" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DN131" s="29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="DO131" s="45" t="n"/>
       <c r="DP131" s="29" t="n">
@@ -58656,13 +58642,13 @@
         <v>2</v>
       </c>
       <c r="DS131" s="46" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT131" s="46" t="n">
-        <v>0.3692</v>
+        <v>0.1605</v>
       </c>
       <c r="DU131" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV131" s="29" t="n">
         <v>0</v>
@@ -58675,16 +58661,12 @@
       </c>
       <c r="DY131" s="31" t="n"/>
       <c r="DZ131" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="EA131" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB131" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="EB131" s="45" t="n"/>
     </row>
     <row r="132">
       <c r="B132" s="14" t="inlineStr">
@@ -58704,12 +58686,12 @@
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>147258</t>
+          <t>101603</t>
         </is>
       </c>
       <c r="F132" s="16" t="inlineStr">
         <is>
-          <t>Nguyễn Bá Mười</t>
+          <t>Trần Minh Trung</t>
         </is>
       </c>
       <c r="G132" s="39" t="inlineStr">
@@ -58726,16 +58708,16 @@
         <v>14</v>
       </c>
       <c r="J132" s="17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K132" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L132" s="40" t="n">
-        <v>114226273</v>
+        <v>118018371</v>
       </c>
       <c r="M132" s="41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N132" s="17" t="n">
         <v>7</v>
@@ -58745,53 +58727,53 @@
         <v>0</v>
       </c>
       <c r="Q132" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R132" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S132" s="43" t="n">
         <v>0.1041</v>
       </c>
       <c r="T132" s="43" t="n">
-        <v>0.1156</v>
+        <v>0.0673</v>
       </c>
       <c r="U132" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V132" s="21" t="n">
         <v>0</v>
       </c>
       <c r="W132" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X132" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y132" s="23" t="n">
-        <v>15856241</v>
+        <v>12832185</v>
       </c>
       <c r="Z132" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA132" s="21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB132" s="39" t="n"/>
       <c r="AC132" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AD132" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE132" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF132" s="43" t="n">
         <v>0.1179</v>
       </c>
       <c r="AG132" s="43" t="n">
-        <v>0.04</v>
+        <v>0.0876</v>
       </c>
       <c r="AH132" s="21" t="n">
         <v>0</v>
@@ -58806,13 +58788,13 @@
         <v>2</v>
       </c>
       <c r="AL132" s="23" t="n">
-        <v>11254417</v>
+        <v>13233417</v>
       </c>
       <c r="AM132" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN132" s="21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO132" s="39" t="n"/>
       <c r="AP132" s="21" t="n">
@@ -58828,7 +58810,7 @@
         <v>0.2487</v>
       </c>
       <c r="AT132" s="43" t="n">
-        <v>0.1386</v>
+        <v>0.2014</v>
       </c>
       <c r="AU132" s="21" t="n">
         <v>0</v>
@@ -58843,7 +58825,7 @@
         <v>2</v>
       </c>
       <c r="AY132" s="23" t="n">
-        <v>15828923</v>
+        <v>17834000</v>
       </c>
       <c r="AZ132" s="24" t="n">
         <v>4</v>
@@ -58878,7 +58860,7 @@
         <v>2</v>
       </c>
       <c r="BL132" s="23" t="n">
-        <v>13872846</v>
+        <v>18120846</v>
       </c>
       <c r="BM132" s="24" t="n">
         <v>4</v>
@@ -58900,7 +58882,7 @@
         <v>0.319</v>
       </c>
       <c r="BT132" s="43" t="n">
-        <v>0.2535</v>
+        <v>0.2866</v>
       </c>
       <c r="BU132" s="21" t="n">
         <v>0</v>
@@ -58915,7 +58897,7 @@
         <v>2</v>
       </c>
       <c r="BY132" s="23" t="n">
-        <v>16930846</v>
+        <v>18926923</v>
       </c>
       <c r="BZ132" s="24" t="n">
         <v>4</v>
@@ -58937,10 +58919,10 @@
         <v>0.1479</v>
       </c>
       <c r="CG132" s="43" t="n">
-        <v>0.1717</v>
+        <v>0.0625</v>
       </c>
       <c r="CH132" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CI132" s="21" t="n">
         <v>0</v>
@@ -58952,19 +58934,15 @@
         <v>2</v>
       </c>
       <c r="CL132" s="23" t="n">
-        <v>20988000</v>
+        <v>19333000</v>
       </c>
       <c r="CM132" s="24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN132" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO132" s="44" t="inlineStr">
-        <is>
-          <t>VƯỢT TRỘI</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="CO132" s="39" t="n"/>
       <c r="CP132" s="21" t="n">
         <v>0</v>
       </c>
@@ -58978,7 +58956,7 @@
         <v>0.3234</v>
       </c>
       <c r="CT132" s="43" t="n">
-        <v>0.2049</v>
+        <v>0.2263</v>
       </c>
       <c r="CU132" s="21" t="n">
         <v>0</v>
@@ -58993,7 +58971,7 @@
         <v>2</v>
       </c>
       <c r="CY132" s="23" t="n">
-        <v>19495000</v>
+        <v>17738000</v>
       </c>
       <c r="CZ132" s="24" t="n">
         <v>4</v>
@@ -59006,16 +58984,16 @@
         <v>0</v>
       </c>
       <c r="DD132" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE132" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DF132" s="43" t="n">
         <v>0.303</v>
       </c>
       <c r="DG132" s="43" t="n">
-        <v>0.2143</v>
+        <v>0.2289</v>
       </c>
       <c r="DH132" s="21" t="n">
         <v>0</v>
@@ -59031,26 +59009,26 @@
       </c>
       <c r="DL132" s="23" t="n"/>
       <c r="DM132" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DN132" s="21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="DO132" s="39" t="n"/>
       <c r="DP132" s="21" t="n">
         <v>0</v>
       </c>
       <c r="DQ132" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR132" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DS132" s="43" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT132" s="43" t="n">
-        <v>0.1443</v>
+        <v>0.2695</v>
       </c>
       <c r="DU132" s="21" t="n">
         <v>0</v>
@@ -59066,10 +59044,10 @@
       </c>
       <c r="DY132" s="23" t="n"/>
       <c r="DZ132" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EA132" s="21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="EB132" s="39" t="n"/>
     </row>
@@ -59428,10 +59406,10 @@
         <v>2</v>
       </c>
       <c r="DS133" s="46" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT133" s="46" t="n">
-        <v>0.3299</v>
+        <v>0.3484</v>
       </c>
       <c r="DU133" s="29" t="n">
         <v>0</v>
@@ -59450,7 +59428,7 @@
         <v>4</v>
       </c>
       <c r="EA133" s="29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="EB133" s="45" t="n"/>
     </row>
@@ -59589,10 +59567,10 @@
         <v>2</v>
       </c>
       <c r="DS134" s="43" t="n">
-        <v>0.3642</v>
+        <v>0.3561</v>
       </c>
       <c r="DT134" s="43" t="n">
-        <v>0.3182</v>
+        <v>0.3291</v>
       </c>
       <c r="DU134" s="21" t="n">
         <v>0</v>
@@ -59611,7 +59589,7 @@
         <v>4</v>
       </c>
       <c r="EA134" s="21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="EB134" s="39" t="n"/>
     </row>
@@ -59924,7 +59902,7 @@
       <c r="DO137" s="8" t="n"/>
       <c r="DP137" s="35" t="inlineStr">
         <is>
-          <t>THÁNG 9 · tới 22/09</t>
+          <t>THÁNG 9</t>
         </is>
       </c>
       <c r="DQ137" s="36" t="n"/>
@@ -62322,7 +62300,7 @@
       </c>
       <c r="C4" s="51" t="inlineStr">
         <is>
-          <t>Lũy kế T1–T9/2026. Tháng 9 chốt data tới 22/09/2026.</t>
+          <t>Lũy kế T1–T9/2026 — Tháng 9 đã chốt đủ tháng (tới 30/09/2026).</t>
         </is>
       </c>
     </row>

--- a/VUOT-TROI-2026.xlsx
+++ b/VUOT-TROI-2026.xlsx
@@ -3075,7 +3075,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>20</v>
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
@@ -3652,9 +3652,15 @@
       <c r="HW6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX6" s="22" t="n"/>
-      <c r="HY6" s="22" t="n"/>
-      <c r="HZ6" s="21" t="n"/>
+      <c r="HX6" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ6" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA6" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -3688,7 +3694,7 @@
         <v>2</v>
       </c>
       <c r="IM6" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="IN6" s="21" t="n">
         <v>1</v>
@@ -3722,7 +3728,9 @@
       </c>
       <c r="IX6" s="22" t="n"/>
       <c r="IY6" s="22" t="n"/>
-      <c r="IZ6" s="21" t="n"/>
+      <c r="IZ6" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA6" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -3756,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="JM6" s="24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="JN6" s="21" t="n">
         <v>1</v>
@@ -3788,7 +3796,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I7" s="17" t="n">
         <v>20</v>
@@ -3803,7 +3811,7 @@
         <v>4</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
@@ -4365,9 +4373,15 @@
       <c r="HW7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX7" s="30" t="n"/>
-      <c r="HY7" s="30" t="n"/>
-      <c r="HZ7" s="29" t="n"/>
+      <c r="HX7" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ7" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA7" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -4401,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="IM7" s="32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="IN7" s="29" t="n">
         <v>1</v>
@@ -4435,7 +4449,9 @@
       </c>
       <c r="IX7" s="30" t="n"/>
       <c r="IY7" s="30" t="n"/>
-      <c r="IZ7" s="29" t="n"/>
+      <c r="IZ7" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA7" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -4469,7 +4485,7 @@
         <v>2</v>
       </c>
       <c r="JM7" s="32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="JN7" s="29" t="n">
         <v>1</v>
@@ -4501,7 +4517,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>20</v>
@@ -4516,7 +4532,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
@@ -5078,9 +5094,15 @@
       <c r="HW8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX8" s="22" t="n"/>
-      <c r="HY8" s="22" t="n"/>
-      <c r="HZ8" s="21" t="n"/>
+      <c r="HX8" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY8" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ8" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA8" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -5114,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="IM8" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="IN8" s="21" t="n">
         <v>1</v>
@@ -5148,7 +5170,9 @@
       </c>
       <c r="IX8" s="22" t="n"/>
       <c r="IY8" s="22" t="n"/>
-      <c r="IZ8" s="21" t="n"/>
+      <c r="IZ8" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA8" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -5182,7 +5206,7 @@
         <v>2</v>
       </c>
       <c r="JM8" s="24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="JN8" s="21" t="n">
         <v>1</v>
@@ -5214,7 +5238,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9" s="17" t="n">
         <v>20</v>
@@ -5229,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="18" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
@@ -5791,9 +5815,15 @@
       <c r="HW9" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX9" s="30" t="n"/>
-      <c r="HY9" s="30" t="n"/>
-      <c r="HZ9" s="29" t="n"/>
+      <c r="HX9" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ9" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA9" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -5827,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="IM9" s="32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="IN9" s="29" t="n">
         <v>4</v>
@@ -5861,7 +5891,9 @@
       </c>
       <c r="IX9" s="30" t="n"/>
       <c r="IY9" s="30" t="n"/>
-      <c r="IZ9" s="29" t="n"/>
+      <c r="IZ9" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA9" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -5893,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="JM9" s="32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JN9" s="29" t="n">
         <v>4</v>
@@ -5925,7 +5957,7 @@
         <v>20</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>20</v>
@@ -5940,7 +5972,7 @@
         <v>2</v>
       </c>
       <c r="M10" s="18" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
@@ -6502,9 +6534,15 @@
       <c r="HW10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX10" s="22" t="n"/>
-      <c r="HY10" s="22" t="n"/>
-      <c r="HZ10" s="21" t="n"/>
+      <c r="HX10" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ10" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA10" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -6538,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="IM10" s="24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="IN10" s="21" t="n">
         <v>6</v>
@@ -6572,7 +6610,9 @@
       </c>
       <c r="IX10" s="22" t="n"/>
       <c r="IY10" s="22" t="n"/>
-      <c r="IZ10" s="21" t="n"/>
+      <c r="IZ10" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA10" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -6606,7 +6646,7 @@
         <v>2</v>
       </c>
       <c r="JM10" s="24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="JN10" s="21" t="n">
         <v>5</v>
@@ -6638,7 +6678,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>20</v>
@@ -6653,7 +6693,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="18" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
@@ -7215,9 +7255,15 @@
       <c r="HW11" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX11" s="30" t="n"/>
-      <c r="HY11" s="30" t="n"/>
-      <c r="HZ11" s="29" t="n"/>
+      <c r="HX11" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ11" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA11" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -7251,7 +7297,7 @@
         <v>2</v>
       </c>
       <c r="IM11" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="IN11" s="29" t="n">
         <v>5</v>
@@ -7285,7 +7331,9 @@
       </c>
       <c r="IX11" s="30" t="n"/>
       <c r="IY11" s="30" t="n"/>
-      <c r="IZ11" s="29" t="n"/>
+      <c r="IZ11" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA11" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -7317,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="JM11" s="32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="JN11" s="29" t="n">
         <v>6</v>
@@ -7349,7 +7397,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>18</v>
@@ -7364,7 +7412,7 @@
         <v>4</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
@@ -7926,9 +7974,15 @@
       <c r="HW12" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX12" s="22" t="n"/>
-      <c r="HY12" s="22" t="n"/>
-      <c r="HZ12" s="21" t="n"/>
+      <c r="HX12" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ12" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA12" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -7962,7 +8016,7 @@
         <v>2</v>
       </c>
       <c r="IM12" s="24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="IN12" s="21" t="n">
         <v>3</v>
@@ -7996,7 +8050,9 @@
       </c>
       <c r="IX12" s="22" t="n"/>
       <c r="IY12" s="22" t="n"/>
-      <c r="IZ12" s="21" t="n"/>
+      <c r="IZ12" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA12" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -8030,7 +8086,7 @@
         <v>2</v>
       </c>
       <c r="JM12" s="24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="JN12" s="21" t="n">
         <v>5</v>
@@ -8062,7 +8118,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I13" s="17" t="n">
         <v>20</v>
@@ -8077,7 +8133,7 @@
         <v>4</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
@@ -8639,9 +8695,15 @@
       <c r="HW13" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX13" s="30" t="n"/>
-      <c r="HY13" s="30" t="n"/>
-      <c r="HZ13" s="29" t="n"/>
+      <c r="HX13" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ13" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA13" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -8675,7 +8737,7 @@
         <v>2</v>
       </c>
       <c r="IM13" s="32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="IN13" s="29" t="n">
         <v>1</v>
@@ -8709,7 +8771,9 @@
       </c>
       <c r="IX13" s="30" t="n"/>
       <c r="IY13" s="30" t="n"/>
-      <c r="IZ13" s="29" t="n"/>
+      <c r="IZ13" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA13" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -8743,7 +8807,7 @@
         <v>2</v>
       </c>
       <c r="JM13" s="32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="JN13" s="29" t="n">
         <v>1</v>
@@ -8775,7 +8839,7 @@
         <v>20</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>20</v>
@@ -8790,7 +8854,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
@@ -9352,9 +9416,15 @@
       <c r="HW14" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX14" s="22" t="n"/>
-      <c r="HY14" s="22" t="n"/>
-      <c r="HZ14" s="21" t="n"/>
+      <c r="HX14" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ14" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA14" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -9388,7 +9458,7 @@
         <v>2</v>
       </c>
       <c r="IM14" s="24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IN14" s="21" t="n">
         <v>5</v>
@@ -9422,7 +9492,9 @@
       </c>
       <c r="IX14" s="22" t="n"/>
       <c r="IY14" s="22" t="n"/>
-      <c r="IZ14" s="21" t="n"/>
+      <c r="IZ14" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA14" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -9454,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="JM14" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="JN14" s="21" t="n">
         <v>3</v>
@@ -9486,7 +9558,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>20</v>
@@ -9501,7 +9573,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
@@ -10063,9 +10135,15 @@
       <c r="HW15" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX15" s="30" t="n"/>
-      <c r="HY15" s="30" t="n"/>
-      <c r="HZ15" s="29" t="n"/>
+      <c r="HX15" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ15" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA15" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -10097,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="IM15" s="32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="IN15" s="29" t="n">
         <v>3</v>
@@ -10131,7 +10209,9 @@
       </c>
       <c r="IX15" s="30" t="n"/>
       <c r="IY15" s="30" t="n"/>
-      <c r="IZ15" s="29" t="n"/>
+      <c r="IZ15" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA15" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -10165,7 +10245,7 @@
         <v>2</v>
       </c>
       <c r="JM15" s="32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="JN15" s="29" t="n">
         <v>1</v>
@@ -10197,7 +10277,7 @@
         <v>20</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I16" s="17" t="n">
         <v>20</v>
@@ -10212,7 +10292,7 @@
         <v>2</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
@@ -10774,9 +10854,15 @@
       <c r="HW16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX16" s="22" t="n"/>
-      <c r="HY16" s="22" t="n"/>
-      <c r="HZ16" s="21" t="n"/>
+      <c r="HX16" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ16" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA16" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -10810,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="IM16" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="IN16" s="21" t="n">
         <v>1</v>
@@ -10844,7 +10930,9 @@
       </c>
       <c r="IX16" s="22" t="n"/>
       <c r="IY16" s="22" t="n"/>
-      <c r="IZ16" s="21" t="n"/>
+      <c r="IZ16" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA16" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -10876,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="JM16" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="JN16" s="21" t="n">
         <v>3</v>
@@ -10908,7 +10996,7 @@
         <v>20</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I17" s="17" t="n">
         <v>20</v>
@@ -10923,7 +11011,7 @@
         <v>2</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
@@ -11485,9 +11573,15 @@
       <c r="HW17" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="HX17" s="30" t="n"/>
-      <c r="HY17" s="30" t="n"/>
-      <c r="HZ17" s="29" t="n"/>
+      <c r="HX17" s="30" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ17" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="IA17" s="28" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -11521,7 +11615,7 @@
         <v>2</v>
       </c>
       <c r="IM17" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="IN17" s="29" t="n">
         <v>7</v>
@@ -11555,7 +11649,9 @@
       </c>
       <c r="IX17" s="30" t="n"/>
       <c r="IY17" s="30" t="n"/>
-      <c r="IZ17" s="29" t="n"/>
+      <c r="IZ17" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="JA17" s="28" t="n">
         <v>9.9</v>
       </c>
@@ -11587,7 +11683,7 @@
         <v>0</v>
       </c>
       <c r="JM17" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="JN17" s="29" t="n">
         <v>7</v>
@@ -11619,7 +11715,7 @@
         <v>20</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>20</v>
@@ -11634,7 +11730,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
@@ -12196,9 +12292,15 @@
       <c r="HW18" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="HX18" s="22" t="n"/>
-      <c r="HY18" s="22" t="n"/>
-      <c r="HZ18" s="21" t="n"/>
+      <c r="HX18" s="22" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="HY18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ18" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="IA18" s="20" t="n">
         <v>9.859999999999999</v>
       </c>
@@ -12230,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="IM18" s="24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="IN18" s="21" t="n">
         <v>6</v>
@@ -12264,7 +12366,9 @@
       </c>
       <c r="IX18" s="22" t="n"/>
       <c r="IY18" s="22" t="n"/>
-      <c r="IZ18" s="21" t="n"/>
+      <c r="IZ18" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="JA18" s="20" t="n">
         <v>9.9</v>
       </c>
@@ -12298,7 +12402,7 @@
         <v>2</v>
       </c>
       <c r="JM18" s="24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="JN18" s="21" t="n">
         <v>5</v>
@@ -70088,7 +70192,7 @@
       </c>
       <c r="C4" s="51" t="inlineStr">
         <is>
-          <t>Lũy kế T1–T10/2026 — Tháng 10 chốt đủ tháng (31/10/2026).</t>
+          <t>Lũy kế T1–T10/2026 — Tháng 10 chốt data tới 25/10/2026 (chưa hết tháng).</t>
         </is>
       </c>
     </row>
